--- a/js/db_Karten.xlsx
+++ b/js/db_Karten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\App_TU_new\js\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Git-projects\TimesUp\js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C17157-8457-4FED-A388-9B2B0FB01DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B361F6E-F0F5-4B66-ABEC-C460FDC3F762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17835" yWindow="345" windowWidth="16200" windowHeight="14850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2832" uniqueCount="2831">
   <si>
     <t>ABBA</t>
   </si>
@@ -4535,13 +4535,3991 @@
   </si>
   <si>
     <t>Ein Zyklop ist ein einäugiges, meist riesiges Fabelwesen der griechischen Mythologie.</t>
+  </si>
+  <si>
+    <t>Axolotl</t>
+  </si>
+  <si>
+    <t>Salamanderart aus Mexiko, bekannt dafür, Gliedmaßen nachwachsen lassen zu können.</t>
+  </si>
+  <si>
+    <t>Wombat</t>
+  </si>
+  <si>
+    <t>Australisches Beuteltier mit gedrungenem Körper und kräftigen Krallen.</t>
+  </si>
+  <si>
+    <t>Tapir</t>
+  </si>
+  <si>
+    <t>Pflanzenfressendes Säugetier mit kurzem rüsselartigem Nasenfortsatz.</t>
+  </si>
+  <si>
+    <t>Ozelot</t>
+  </si>
+  <si>
+    <t>Kleine gefleckte Wildkatze aus Mittel- und Südamerika.</t>
+  </si>
+  <si>
+    <t>Kondor</t>
+  </si>
+  <si>
+    <t>Sehr großer Greifvogel der Anden mit enormer Flügelspannweite.</t>
+  </si>
+  <si>
+    <t>Kaiserpinguin</t>
+  </si>
+  <si>
+    <t>Größte Pinguinart, die in der Antarktis brütet.</t>
+  </si>
+  <si>
+    <t>Seeanemone</t>
+  </si>
+  <si>
+    <t>Meerestier, das wie eine Blume aussieht und mit Tentakeln Beute fängt.</t>
+  </si>
+  <si>
+    <t>Seegurke</t>
+  </si>
+  <si>
+    <t>Weiches Meerestier aus der Gruppe der Stachelhäuter.</t>
+  </si>
+  <si>
+    <t>Feuerfisch</t>
+  </si>
+  <si>
+    <t>Bunter, giftiger Meeresfisch mit fächerartigen Flossen.</t>
+  </si>
+  <si>
+    <t>Hammerhai</t>
+  </si>
+  <si>
+    <t>Haiart mit auffällig verbreitertem Kopf in Hammerform.</t>
+  </si>
+  <si>
+    <t>Mantarochen</t>
+  </si>
+  <si>
+    <t>Großer Rochen mit flügelartigen Brustflossen.</t>
+  </si>
+  <si>
+    <t>Kugelfisch</t>
+  </si>
+  <si>
+    <t>Fisch, der sich bei Gefahr kugelförmig aufblasen kann.</t>
+  </si>
+  <si>
+    <t>Pfau</t>
+  </si>
+  <si>
+    <t>Vogel, dessen Männchen ein farbenprächtiges Rad aus Schwanzfedern zeigen.</t>
+  </si>
+  <si>
+    <t>Kolibri</t>
+  </si>
+  <si>
+    <t>Sehr kleiner Vogel, der in der Luft schweben und rückwärts fliegen kann.</t>
+  </si>
+  <si>
+    <t>Nacktmull</t>
+  </si>
+  <si>
+    <t>Fast haarloses Nagetier, das in unterirdischen Kolonien lebt.</t>
+  </si>
+  <si>
+    <t>Alpaka</t>
+  </si>
+  <si>
+    <t>Domestiziertes Andenkamel, dessen Wolle genutzt wird.</t>
+  </si>
+  <si>
+    <t>Lama</t>
+  </si>
+  <si>
+    <t>Südamerikanisches Lasttier, das mit Alpakas verwandt ist.</t>
+  </si>
+  <si>
+    <t>Gürteltier</t>
+  </si>
+  <si>
+    <t>Säugetier mit gepanzertem Rücken, das sich teilweise einrollen kann.</t>
+  </si>
+  <si>
+    <t>Komodowaran</t>
+  </si>
+  <si>
+    <t>Größte Echse der Welt, heimisch auf indonesischen Inseln.</t>
+  </si>
+  <si>
+    <t>Leguan</t>
+  </si>
+  <si>
+    <t>Große Echse, häufig mit Rückenkamm und langem Schwanz.</t>
+  </si>
+  <si>
+    <t>Gecko</t>
+  </si>
+  <si>
+    <t>Kleine Echse, die dank Haftlamellen an Wänden laufen kann.</t>
+  </si>
+  <si>
+    <t>Chamäleon</t>
+  </si>
+  <si>
+    <t>Echse, die ihre Farbe ändern und die Augen unabhängig bewegen kann.</t>
+  </si>
+  <si>
+    <t>Flughund</t>
+  </si>
+  <si>
+    <t>Große fruchtfressende Fledermaus mit hundeähnlichem Kopf.</t>
+  </si>
+  <si>
+    <t>Orang-Utan</t>
+  </si>
+  <si>
+    <t>Menschenaffe aus Südostasien, der viel Zeit in Bäumen verbringt.</t>
+  </si>
+  <si>
+    <t>Bonobo</t>
+  </si>
+  <si>
+    <t>Menschenaffe aus Zentralafrika, eng mit dem Schimpansen verwandt.</t>
+  </si>
+  <si>
+    <t>Kapuzineraffe</t>
+  </si>
+  <si>
+    <t>Kleiner intelligenter Affe aus Mittel- und Südamerika.</t>
+  </si>
+  <si>
+    <t>Faultier</t>
+  </si>
+  <si>
+    <t>Langsames baumbewohnendes Säugetier aus Mittel- und Südamerika.</t>
+  </si>
+  <si>
+    <t>Ameisenbär</t>
+  </si>
+  <si>
+    <t>Säugetier mit langer Schnauze und klebriger Zunge zum Fressen von Ameisen.</t>
+  </si>
+  <si>
+    <t>Waschbär</t>
+  </si>
+  <si>
+    <t>Kleines Raubtier mit maskenartiger Gesichtszeichnung und geschickten Pfoten.</t>
+  </si>
+  <si>
+    <t>Dachs</t>
+  </si>
+  <si>
+    <t>Kräftiges, grabendes Raubtier mit schwarz-weißem Kopfstreifen.</t>
+  </si>
+  <si>
+    <t>Hermelin</t>
+  </si>
+  <si>
+    <t>Kleines Raubtier aus der Marderfamilie mit weißem Winterfell.</t>
+  </si>
+  <si>
+    <t>Iltis</t>
+  </si>
+  <si>
+    <t>Marderart, die mit dem Frettchen verwandt ist.</t>
+  </si>
+  <si>
+    <t>Murmeltier</t>
+  </si>
+  <si>
+    <t>Nagetiere der Alpen und Steppen, bekannt für Warnpfiffe.</t>
+  </si>
+  <si>
+    <t>Biber</t>
+  </si>
+  <si>
+    <t>Nagetier, das Dämme baut und Bäume annagt.</t>
+  </si>
+  <si>
+    <t>Otter</t>
+  </si>
+  <si>
+    <t>Wasserliebendes Raubtier mit dichtem Fell und spielerischem Verhalten.</t>
+  </si>
+  <si>
+    <t>Seelöwe</t>
+  </si>
+  <si>
+    <t>Meeressäuger mit äußeren Ohren, der sich an Land gut fortbewegen kann.</t>
+  </si>
+  <si>
+    <t>Walross</t>
+  </si>
+  <si>
+    <t>Großer Meeressäuger mit langen Stoßzähnen und Schnurrhaaren.</t>
+  </si>
+  <si>
+    <t>Buckelwal</t>
+  </si>
+  <si>
+    <t>Walart, bekannt für Gesänge und Sprünge aus dem Wasser.</t>
+  </si>
+  <si>
+    <t>Pottwal</t>
+  </si>
+  <si>
+    <t>Zahnwal mit großem Kopf, der sehr tief tauchen kann.</t>
+  </si>
+  <si>
+    <t>Seekuh</t>
+  </si>
+  <si>
+    <t>Pflanzenfressender Meeressäuger mit rundlichem Körper.</t>
+  </si>
+  <si>
+    <t>Hyäne</t>
+  </si>
+  <si>
+    <t>Raubtier mit starkem Kiefer und lachähnlichen Lauten.</t>
+  </si>
+  <si>
+    <t>Luchs</t>
+  </si>
+  <si>
+    <t>Wildkatze mit Pinselohren und kurzem Schwanz.</t>
+  </si>
+  <si>
+    <t>Schneeleopard</t>
+  </si>
+  <si>
+    <t>Große Wildkatze aus Hochgebirgen Zentralasiens.</t>
+  </si>
+  <si>
+    <t>Jaguar</t>
+  </si>
+  <si>
+    <t>Große gefleckte Katze aus Amerika mit sehr kräftigem Biss.</t>
+  </si>
+  <si>
+    <t>Puma</t>
+  </si>
+  <si>
+    <t>Große Wildkatze Amerikas, auch Berglöwe genannt.</t>
+  </si>
+  <si>
+    <t>Gepard</t>
+  </si>
+  <si>
+    <t>Schnellstes Landtier, erkennbar an Tränenstreifen im Gesicht.</t>
+  </si>
+  <si>
+    <t>Antilope</t>
+  </si>
+  <si>
+    <t>Schnelles Huftier mit Hörnern, häufig in afrikanischen Savannen.</t>
+  </si>
+  <si>
+    <t>Gazelle</t>
+  </si>
+  <si>
+    <t>Schlanke Antilopenart, bekannt für hohe Sprünge.</t>
+  </si>
+  <si>
+    <t>Gnu</t>
+  </si>
+  <si>
+    <t>Große Antilope, bekannt für Wanderungen in Ostafrika.</t>
+  </si>
+  <si>
+    <t>Elch</t>
+  </si>
+  <si>
+    <t>Größte Hirschart mit breitem Schaufelgeweih.</t>
+  </si>
+  <si>
+    <t>Rentier</t>
+  </si>
+  <si>
+    <t>Hirschart aus nördlichen Regionen, bei der beide Geschlechter Geweihe tragen.</t>
+  </si>
+  <si>
+    <t>Bison</t>
+  </si>
+  <si>
+    <t>Großes Wildrind Nordamerikas mit mächtigem Schulterhöcker.</t>
+  </si>
+  <si>
+    <t>Wasserbüffel</t>
+  </si>
+  <si>
+    <t>Großes Rind, das oft in Reisfeldern eingesetzt wird.</t>
+  </si>
+  <si>
+    <t>Warzenschwein</t>
+  </si>
+  <si>
+    <t>Afrikanisches Wildschwein mit Gesichtshöckern und Hauern.</t>
+  </si>
+  <si>
+    <t>Erdferkel</t>
+  </si>
+  <si>
+    <t>Afrikanisches Säugetier, das Termiten frisst und Höhlen gräbt.</t>
+  </si>
+  <si>
+    <t>Nasenbär</t>
+  </si>
+  <si>
+    <t>Kletterndes Säugetier aus Amerika mit langer beweglicher Schnauze.</t>
+  </si>
+  <si>
+    <t>Tasmanischer Teufel</t>
+  </si>
+  <si>
+    <t>Raubbeutler aus Tasmanien mit kräftigem Gebiss.</t>
+  </si>
+  <si>
+    <t>Schnabeltier</t>
+  </si>
+  <si>
+    <t>Eierlegendes Säugetier aus Australien mit Schnabel und Schwimmhäuten.</t>
+  </si>
+  <si>
+    <t>Anakonda</t>
+  </si>
+  <si>
+    <t>Sehr große Würgeschlange aus Südamerika.</t>
+  </si>
+  <si>
+    <t>Kobra</t>
+  </si>
+  <si>
+    <t>Giftschlange, die bei Bedrohung eine Halskrause aufstellt.</t>
+  </si>
+  <si>
+    <t>Klapperschlange</t>
+  </si>
+  <si>
+    <t>Giftschlange mit rasselndem Schwanzende.</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Große Würgeschlange, die Beute umschlingt.</t>
+  </si>
+  <si>
+    <t>Boa constrictor</t>
+  </si>
+  <si>
+    <t>Große Würgeschlange aus Amerika.</t>
+  </si>
+  <si>
+    <t>Salamander</t>
+  </si>
+  <si>
+    <t>Amphibium mit langem Körper und Schwanz.</t>
+  </si>
+  <si>
+    <t>Molch</t>
+  </si>
+  <si>
+    <t>Kleines Amphibium, das oft im Wasser lebt.</t>
+  </si>
+  <si>
+    <t>Laubfrosch</t>
+  </si>
+  <si>
+    <t>Kleiner grüner Frosch, der gut klettern kann.</t>
+  </si>
+  <si>
+    <t>Pfeilgiftfrosch</t>
+  </si>
+  <si>
+    <t>Sehr farbenfroher Frosch mit giftiger Haut.</t>
+  </si>
+  <si>
+    <t>Kröte</t>
+  </si>
+  <si>
+    <t>Amphibium mit warziger Haut und kurzem Sprung.</t>
+  </si>
+  <si>
+    <t>Alligator</t>
+  </si>
+  <si>
+    <t>Krokodilähnliches Reptil mit breiter Schnauze.</t>
+  </si>
+  <si>
+    <t>Seepferdchen</t>
+  </si>
+  <si>
+    <t>Kleiner Fisch mit pferdeähnlichem Kopf.</t>
+  </si>
+  <si>
+    <t>Clownfisch</t>
+  </si>
+  <si>
+    <t>Orange-weißer Rifffisch, der oft mit Anemonen lebt.</t>
+  </si>
+  <si>
+    <t>Zitteraal</t>
+  </si>
+  <si>
+    <t>Fisch, der elektrische Schläge erzeugen kann.</t>
+  </si>
+  <si>
+    <t>Muräne</t>
+  </si>
+  <si>
+    <t>Schlangenförmiger Meeresfisch, der in Riffspalten lebt.</t>
+  </si>
+  <si>
+    <t>Makrele</t>
+  </si>
+  <si>
+    <t>Schneller Schwarmfisch mit gestreiftem Rücken.</t>
+  </si>
+  <si>
+    <t>Karpfen</t>
+  </si>
+  <si>
+    <t>Süßwasserfisch, der häufig in Teichen gehalten wird.</t>
+  </si>
+  <si>
+    <t>Hecht</t>
+  </si>
+  <si>
+    <t>Raubfisch mit langem Körper und spitzen Zähnen.</t>
+  </si>
+  <si>
+    <t>Stör</t>
+  </si>
+  <si>
+    <t>Altertümlich wirkender Fisch, dessen Rogen als Kaviar genutzt wird.</t>
+  </si>
+  <si>
+    <t>Seestern</t>
+  </si>
+  <si>
+    <t>Meerestier mit meist fünf Armen.</t>
+  </si>
+  <si>
+    <t>Tintenfisch</t>
+  </si>
+  <si>
+    <t>Weichtier mit Fangarmen und Tintenbeutel.</t>
+  </si>
+  <si>
+    <t>Krake</t>
+  </si>
+  <si>
+    <t>Intelligentes Weichtier mit acht Armen.</t>
+  </si>
+  <si>
+    <t>Nautilus</t>
+  </si>
+  <si>
+    <t>Meerestier mit spiraliger Schale und vielen Tentakeln.</t>
+  </si>
+  <si>
+    <t>Libelle</t>
+  </si>
+  <si>
+    <t>Insekt mit großen Augen und zwei Paar durchsichtigen Flügeln.</t>
+  </si>
+  <si>
+    <t>Gottesanbeterin</t>
+  </si>
+  <si>
+    <t>Insekt mit fangartig angewinkelten Vorderbeinen.</t>
+  </si>
+  <si>
+    <t>Marienkäfer</t>
+  </si>
+  <si>
+    <t>Kleiner Käfer mit Punkten, gilt oft als Glückssymbol.</t>
+  </si>
+  <si>
+    <t>Hirschkäfer</t>
+  </si>
+  <si>
+    <t>Großer Käfer, dessen Männchen geweihartige Kiefer haben.</t>
+  </si>
+  <si>
+    <t>Glühwürmchen</t>
+  </si>
+  <si>
+    <t>Käfer, der Lichtsignale erzeugt.</t>
+  </si>
+  <si>
+    <t>Borkenkäfer</t>
+  </si>
+  <si>
+    <t>Käfer, der unter Baumrinde lebt und Wälder schädigen kann.</t>
+  </si>
+  <si>
+    <t>Maulwurfsgrille</t>
+  </si>
+  <si>
+    <t>Grabendes Insekt mit schaufelartigen Vorderbeinen.</t>
+  </si>
+  <si>
+    <t>Skorpion</t>
+  </si>
+  <si>
+    <t>Spinnentier mit Scheren und giftigem Schwanzstachel.</t>
+  </si>
+  <si>
+    <t>Tarantel</t>
+  </si>
+  <si>
+    <t>Große haarige Spinne.</t>
+  </si>
+  <si>
+    <t>Weberknecht</t>
+  </si>
+  <si>
+    <t>Spinnentier mit sehr langen dünnen Beinen.</t>
+  </si>
+  <si>
+    <t>Seidenspinner</t>
+  </si>
+  <si>
+    <t>Schmetterlingsraupe, aus deren Kokon Seide gewonnen wird.</t>
+  </si>
+  <si>
+    <t>Motte</t>
+  </si>
+  <si>
+    <t>Nachtaktiver Schmetterling, manche Arten fressen Textilien.</t>
+  </si>
+  <si>
+    <t>Ramen</t>
+  </si>
+  <si>
+    <t>Japanische Nudelsuppe mit Brühe, Nudeln und verschiedenen Beilagen.</t>
+  </si>
+  <si>
+    <t>Falafel</t>
+  </si>
+  <si>
+    <t>Frittierte Bällchen aus Kichererbsen oder Bohnen.</t>
+  </si>
+  <si>
+    <t>Hummus</t>
+  </si>
+  <si>
+    <t>Cremiger Dip aus Kichererbsen, Sesam, Öl und Zitrone.</t>
+  </si>
+  <si>
+    <t>Couscous</t>
+  </si>
+  <si>
+    <t>Kleine gedämpfte Hartweizengrieß-Kügelchen, oft als Beilage.</t>
+  </si>
+  <si>
+    <t>Bulgur</t>
+  </si>
+  <si>
+    <t>Vorgegarter Weizenschrot, häufig in Salaten und orientalischen Gerichten.</t>
+  </si>
+  <si>
+    <t>Gnocchi</t>
+  </si>
+  <si>
+    <t>Kleine italienische Klößchen, meist aus Kartoffelteig.</t>
+  </si>
+  <si>
+    <t>Risotto</t>
+  </si>
+  <si>
+    <t>Cremiges italienisches Reisgericht, das unter Rühren gekocht wird.</t>
+  </si>
+  <si>
+    <t>Lasagne</t>
+  </si>
+  <si>
+    <t>Schichtgericht aus Nudelplatten, Soße und Käse.</t>
+  </si>
+  <si>
+    <t>Bruschetta</t>
+  </si>
+  <si>
+    <t>Geröstetes Brot mit Tomaten, Knoblauch und Olivenöl.</t>
+  </si>
+  <si>
+    <t>Tiramisu</t>
+  </si>
+  <si>
+    <t>Italienisches Dessert aus Mascarpone, Kaffee und Löffelbiskuits.</t>
+  </si>
+  <si>
+    <t>Panna Cotta</t>
+  </si>
+  <si>
+    <t>Italienisches Sahnedessert, das mit Gelatine gestockt wird.</t>
+  </si>
+  <si>
+    <t>Cannoli</t>
+  </si>
+  <si>
+    <t>Sizilianisches Gebäck mit cremiger Füllung.</t>
+  </si>
+  <si>
+    <t>Paella</t>
+  </si>
+  <si>
+    <t>Spanisches Reisgericht, oft mit Safran, Gemüse, Fleisch oder Meeresfrüchten.</t>
+  </si>
+  <si>
+    <t>Gazpacho</t>
+  </si>
+  <si>
+    <t>Kalte spanische Suppe aus rohem Gemüse, vor allem Tomaten.</t>
+  </si>
+  <si>
+    <t>Churros</t>
+  </si>
+  <si>
+    <t>Frittiertes spanisches Gebäck, oft mit Zucker und Schokolade.</t>
+  </si>
+  <si>
+    <t>Tapas</t>
+  </si>
+  <si>
+    <t>Kleine spanische Häppchen, die gemeinsam geteilt werden.</t>
+  </si>
+  <si>
+    <t>Guacamole</t>
+  </si>
+  <si>
+    <t>Mexikanischer Avocado-Dip mit Limette, Zwiebeln und Gewürzen.</t>
+  </si>
+  <si>
+    <t>Burrito</t>
+  </si>
+  <si>
+    <t>Gefüllte Tortilla-Rolle mit Reis, Bohnen, Fleisch oder Gemüse.</t>
+  </si>
+  <si>
+    <t>Nachos</t>
+  </si>
+  <si>
+    <t>Tortilla-Chips, häufig mit Käse oder Dips serviert.</t>
+  </si>
+  <si>
+    <t>Enchilada</t>
+  </si>
+  <si>
+    <t>Gefüllte Tortilla, die mit Soße überbacken wird.</t>
+  </si>
+  <si>
+    <t>Arepa</t>
+  </si>
+  <si>
+    <t>Maisfladen aus Venezuela oder Kolumbien, oft gefüllt.</t>
+  </si>
+  <si>
+    <t>Bagel</t>
+  </si>
+  <si>
+    <t>Ringförmiges Gebäck, das vor dem Backen kurz gekocht wird.</t>
+  </si>
+  <si>
+    <t>Brownie</t>
+  </si>
+  <si>
+    <t>Saftiger Schokoladenkuchen in kleinen Stücken.</t>
+  </si>
+  <si>
+    <t>Cheesecake</t>
+  </si>
+  <si>
+    <t>Käsekuchen, oft mit Frischkäse und Keksboden.</t>
+  </si>
+  <si>
+    <t>Cupcake</t>
+  </si>
+  <si>
+    <t>Kleiner Kuchen in Papierförmchen mit Cremehaube.</t>
+  </si>
+  <si>
+    <t>Waffle</t>
+  </si>
+  <si>
+    <t>Gebäck aus Waffelteig mit typischem Muster.</t>
+  </si>
+  <si>
+    <t>Fish and Chips</t>
+  </si>
+  <si>
+    <t>Britisches Gericht aus frittiertem Fisch und Pommes.</t>
+  </si>
+  <si>
+    <t>Haggis</t>
+  </si>
+  <si>
+    <t>Schottisches Gericht aus gewürztem Schafsinneren und Hafer.</t>
+  </si>
+  <si>
+    <t>Fondue</t>
+  </si>
+  <si>
+    <t>Gericht, bei dem Speisen in geschmolzenen Käse oder heiße Flüssigkeit getaucht werden.</t>
+  </si>
+  <si>
+    <t>Raclette</t>
+  </si>
+  <si>
+    <t>Schweizer Käsegericht, bei dem geschmolzener Käse mit Beilagen gegessen wird.</t>
+  </si>
+  <si>
+    <t>Rösti</t>
+  </si>
+  <si>
+    <t>Schweizer Kartoffelgericht aus geriebenen, gebratenen Kartoffeln.</t>
+  </si>
+  <si>
+    <t>Gulasch</t>
+  </si>
+  <si>
+    <t>Würziger Eintopf aus Fleisch, Paprika und Zwiebeln.</t>
+  </si>
+  <si>
+    <t>Baklava</t>
+  </si>
+  <si>
+    <t>Süßes Gebäck aus Filoteig, Nüssen und Sirup.</t>
+  </si>
+  <si>
+    <t>Kebab</t>
+  </si>
+  <si>
+    <t>Gegrilltes oder gebratenes Fleischgericht aus dem Nahen Osten.</t>
+  </si>
+  <si>
+    <t>Dönerbox</t>
+  </si>
+  <si>
+    <t>Imbissgericht mit Dönerfleisch, Pommes oder Reis und Soße.</t>
+  </si>
+  <si>
+    <t>Lahmacun</t>
+  </si>
+  <si>
+    <t>Dünner türkischer Fladen mit würziger Hackfleischschicht.</t>
+  </si>
+  <si>
+    <t>Börek</t>
+  </si>
+  <si>
+    <t>Gefülltes Teiggebäck aus der türkischen und Balkanküche.</t>
+  </si>
+  <si>
+    <t>Köfte</t>
+  </si>
+  <si>
+    <t>Gewürzte Hackfleischbällchen oder -röllchen.</t>
+  </si>
+  <si>
+    <t>Ayran</t>
+  </si>
+  <si>
+    <t>Türkisches Joghurtgetränk mit Wasser und Salz.</t>
+  </si>
+  <si>
+    <t>Butter Chicken</t>
+  </si>
+  <si>
+    <t>Indisches Hähnchengericht in cremiger Tomatensoße.</t>
+  </si>
+  <si>
+    <t>Matcha</t>
+  </si>
+  <si>
+    <t>Fein gemahlenes grünes Teepulver aus Japan.</t>
+  </si>
+  <si>
+    <t>Bubble Tea</t>
+  </si>
+  <si>
+    <t>Teegetränk mit Milch oder Fruchtgeschmack und Tapiokaperlen.</t>
+  </si>
+  <si>
+    <t>Smoothie Bowl</t>
+  </si>
+  <si>
+    <t>Dickflüssiger Smoothie in einer Schüssel mit Toppings.</t>
+  </si>
+  <si>
+    <t>Avocadotoast</t>
+  </si>
+  <si>
+    <t>Toastbrot mit Avocado, oft mit Gewürzen oder Ei.</t>
+  </si>
+  <si>
+    <t>Pesto</t>
+  </si>
+  <si>
+    <t>Italienische Kräuterpaste, meist aus Basilikum, Öl, Nüssen und Käse.</t>
+  </si>
+  <si>
+    <t>Sauerteigbrot</t>
+  </si>
+  <si>
+    <t>Brot, das mit natürlichem Sauerteig gelockert wird.</t>
+  </si>
+  <si>
+    <t>Brezel</t>
+  </si>
+  <si>
+    <t>Verschlungenes Laugengebäck mit Salz.</t>
+  </si>
+  <si>
+    <t>Kaiserschmarrn</t>
+  </si>
+  <si>
+    <t>Zerrissener süßer Pfannkuchen aus Österreich.</t>
+  </si>
+  <si>
+    <t>Sachertorte</t>
+  </si>
+  <si>
+    <t>Wiener Schokoladentorte mit Aprikosenmarmelade.</t>
+  </si>
+  <si>
+    <t>Apfelstrudel</t>
+  </si>
+  <si>
+    <t>Österreichisches Gebäck aus dünnem Teig mit Apfelfüllung.</t>
+  </si>
+  <si>
+    <t>Schwarzwälder Kirschtorte</t>
+  </si>
+  <si>
+    <t>Sahnetorte mit Schokolade, Kirschen und Kirschwasser.</t>
+  </si>
+  <si>
+    <t>Maultaschen</t>
+  </si>
+  <si>
+    <t>Gefüllte schwäbische Teigtaschen.</t>
+  </si>
+  <si>
+    <t>Spätzle</t>
+  </si>
+  <si>
+    <t>Schwäbische Eiernudeln, oft als Beilage.</t>
+  </si>
+  <si>
+    <t>Flammkuchen</t>
+  </si>
+  <si>
+    <t>Dünner Teigfladen mit Creme, Zwiebeln und Speck.</t>
+  </si>
+  <si>
+    <t>Zwiebelkuchen</t>
+  </si>
+  <si>
+    <t>Herzhafter Kuchen mit Zwiebelbelag.</t>
+  </si>
+  <si>
+    <t>Grünkohl</t>
+  </si>
+  <si>
+    <t>Wintergemüse, häufig als deftiges Gericht mit Wurst serviert.</t>
+  </si>
+  <si>
+    <t>Kartoffelpuffer</t>
+  </si>
+  <si>
+    <t>In der Pfanne gebratene Reibekuchen aus Kartoffeln.</t>
+  </si>
+  <si>
+    <t>Milchreis</t>
+  </si>
+  <si>
+    <t>Süßes Reisgericht, das in Milch gekocht wird.</t>
+  </si>
+  <si>
+    <t>Grießbrei</t>
+  </si>
+  <si>
+    <t>Warmer Brei aus Grieß und Milch.</t>
+  </si>
+  <si>
+    <t>Marmorkuchen</t>
+  </si>
+  <si>
+    <t>Kuchen mit hellem und dunklem Teig in Marmoroptik.</t>
+  </si>
+  <si>
+    <t>Bienenstich</t>
+  </si>
+  <si>
+    <t>Kuchen mit Cremefüllung und Mandel-Honig-Belag.</t>
+  </si>
+  <si>
+    <t>Käsefondue</t>
+  </si>
+  <si>
+    <t>Fonduevariante mit geschmolzenem Käse.</t>
+  </si>
+  <si>
+    <t>Kartoffelsalat</t>
+  </si>
+  <si>
+    <t>Salat aus Kartoffelscheiben, je nach Region mit Brühe oder Mayonnaise.</t>
+  </si>
+  <si>
+    <t>Nudelsalat</t>
+  </si>
+  <si>
+    <t>Kalter Salat aus Nudeln, Gemüse und Dressing.</t>
+  </si>
+  <si>
+    <t>Linsensuppe</t>
+  </si>
+  <si>
+    <t>Suppe aus Linsen, oft mit Gemüse und Würstchen.</t>
+  </si>
+  <si>
+    <t>Erbseneintopf</t>
+  </si>
+  <si>
+    <t>Sämiger Eintopf aus Erbsen und Gemüse.</t>
+  </si>
+  <si>
+    <t>Ofenkartoffel</t>
+  </si>
+  <si>
+    <t>Im Ofen gegarte Kartoffel, oft mit Kräuterquark.</t>
+  </si>
+  <si>
+    <t>Bratkartoffeln</t>
+  </si>
+  <si>
+    <t>Gebratene Kartoffelscheiben, oft mit Zwiebeln und Speck.</t>
+  </si>
+  <si>
+    <t>Rührei</t>
+  </si>
+  <si>
+    <t>In der Pfanne gestockte und verrührte Eier.</t>
+  </si>
+  <si>
+    <t>Spiegelei</t>
+  </si>
+  <si>
+    <t>In der Pfanne gebratenes Ei mit sichtbarem Dotter.</t>
+  </si>
+  <si>
+    <t>Omelett</t>
+  </si>
+  <si>
+    <t>Eierspeise, die in der Pfanne gebacken und oft gefüllt wird.</t>
+  </si>
+  <si>
+    <t>Kräuterquark</t>
+  </si>
+  <si>
+    <t>Quark mit frischen Kräutern, oft als Dip zu Kartoffeln.</t>
+  </si>
+  <si>
+    <t>Tomatensuppe</t>
+  </si>
+  <si>
+    <t>Suppe aus Tomaten, oft cremig oder mit Kräutern.</t>
+  </si>
+  <si>
+    <t>Kürbissuppe</t>
+  </si>
+  <si>
+    <t>Cremige Suppe aus Kürbis, häufig im Herbst.</t>
+  </si>
+  <si>
+    <t>Gemüseauflauf</t>
+  </si>
+  <si>
+    <t>Überbackenes Gericht aus verschiedenen Gemüsesorten.</t>
+  </si>
+  <si>
+    <t>Nudelauflauf</t>
+  </si>
+  <si>
+    <t>Überbackenes Gericht mit Nudeln, Soße und Käse.</t>
+  </si>
+  <si>
+    <t>Reispfanne</t>
+  </si>
+  <si>
+    <t>Gericht aus Reis, Gemüse und weiteren Zutaten aus der Pfanne.</t>
+  </si>
+  <si>
+    <t>Akkuschrauber</t>
+  </si>
+  <si>
+    <t>Elektrisches Werkzeug zum Schrauben und Bohren mit wiederaufladbarem Akku.</t>
+  </si>
+  <si>
+    <t>Angelrute</t>
+  </si>
+  <si>
+    <t>Langer Stab mit Schnur und Haken zum Angeln.</t>
+  </si>
+  <si>
+    <t>Anschnallgurt</t>
+  </si>
+  <si>
+    <t>Sicherheitsgurt im Fahrzeug zum Schutz bei Unfällen.</t>
+  </si>
+  <si>
+    <t>Aquarium</t>
+  </si>
+  <si>
+    <t>Glasbehälter für Fische, Wasserpflanzen und andere Wasserlebewesen.</t>
+  </si>
+  <si>
+    <t>Armbanduhr</t>
+  </si>
+  <si>
+    <t>Uhr, die am Handgelenk getragen wird.</t>
+  </si>
+  <si>
+    <t>Ausweis</t>
+  </si>
+  <si>
+    <t>Dokument, das die Identität einer Person bestätigt.</t>
+  </si>
+  <si>
+    <t>Backform</t>
+  </si>
+  <si>
+    <t>Form, in der Kuchen oder Brot gebacken wird.</t>
+  </si>
+  <si>
+    <t>Badewanne</t>
+  </si>
+  <si>
+    <t>Große Wanne zum Baden.</t>
+  </si>
+  <si>
+    <t>Bagger</t>
+  </si>
+  <si>
+    <t>Baumaschine mit Schaufel zum Graben und Bewegen von Erde.</t>
+  </si>
+  <si>
+    <t>Balkon</t>
+  </si>
+  <si>
+    <t>Plattform an einem Gebäude, die nach außen ragt.</t>
+  </si>
+  <si>
+    <t>Barhocker</t>
+  </si>
+  <si>
+    <t>Hoher Stuhl, oft an Theken oder Bars.</t>
+  </si>
+  <si>
+    <t>Batterieladegerät</t>
+  </si>
+  <si>
+    <t>Gerät zum Wiederaufladen von Akkus oder Batterien.</t>
+  </si>
+  <si>
+    <t>Bauhelm</t>
+  </si>
+  <si>
+    <t>Schutzhelm auf Baustellen.</t>
+  </si>
+  <si>
+    <t>Beamer</t>
+  </si>
+  <si>
+    <t>Projektor, der Bilder oder Videos auf eine Leinwand wirft.</t>
+  </si>
+  <si>
+    <t>Bettdecke</t>
+  </si>
+  <si>
+    <t>Decke, unter der man im Bett schläft.</t>
+  </si>
+  <si>
+    <t>Bilderrahmen</t>
+  </si>
+  <si>
+    <t>Rahmen zum Aufhängen oder Aufstellen von Bildern.</t>
+  </si>
+  <si>
+    <t>Blumentopf</t>
+  </si>
+  <si>
+    <t>Gefäß, in dem Pflanzen wachsen.</t>
+  </si>
+  <si>
+    <t>Briefkasten</t>
+  </si>
+  <si>
+    <t>Kasten, in den Post eingeworfen wird.</t>
+  </si>
+  <si>
+    <t>Bügeleisen</t>
+  </si>
+  <si>
+    <t>Gerät zum Glätten von Kleidung mit Hitze.</t>
+  </si>
+  <si>
+    <t>Büroklammer</t>
+  </si>
+  <si>
+    <t>Kleiner Drahtclip zum Zusammenhalten von Papier.</t>
+  </si>
+  <si>
+    <t>Campingkocher</t>
+  </si>
+  <si>
+    <t>Kleiner tragbarer Kocher für unterwegs.</t>
+  </si>
+  <si>
+    <t>Couchkissen</t>
+  </si>
+  <si>
+    <t>Kissen, das auf dem Sofa liegt.</t>
+  </si>
+  <si>
+    <t>Dachrinne</t>
+  </si>
+  <si>
+    <t>Rinne am Dach, die Regenwasser ableitet.</t>
+  </si>
+  <si>
+    <t>Dampfbügeleisen</t>
+  </si>
+  <si>
+    <t>Bügeleisen, das zusätzlich Dampf abgibt.</t>
+  </si>
+  <si>
+    <t>Dartpfeil</t>
+  </si>
+  <si>
+    <t>Kleiner Wurfpfeil für das Dartspiel.</t>
+  </si>
+  <si>
+    <t>Deckenlampe</t>
+  </si>
+  <si>
+    <t>Lampe, die an der Zimmerdecke befestigt ist.</t>
+  </si>
+  <si>
+    <t>Dosenöffner</t>
+  </si>
+  <si>
+    <t>Werkzeug zum Öffnen von Konservendosen.</t>
+  </si>
+  <si>
+    <t>Drehstuhl</t>
+  </si>
+  <si>
+    <t>Stuhl mit drehbarer Sitzfläche, oft im Büro.</t>
+  </si>
+  <si>
+    <t>Druckerpatrone</t>
+  </si>
+  <si>
+    <t>Behälter mit Tinte oder Toner für einen Drucker.</t>
+  </si>
+  <si>
+    <t>Duschkopf</t>
+  </si>
+  <si>
+    <t>Teil der Dusche, aus dem Wasser austritt.</t>
+  </si>
+  <si>
+    <t>Eierbecher</t>
+  </si>
+  <si>
+    <t>Kleines Gefäß für ein gekochtes Ei.</t>
+  </si>
+  <si>
+    <t>Einkaufswagen</t>
+  </si>
+  <si>
+    <t>Rollbarer Wagen im Supermarkt.</t>
+  </si>
+  <si>
+    <t>Eiswürfelform</t>
+  </si>
+  <si>
+    <t>Form zum Herstellen von Eiswürfeln.</t>
+  </si>
+  <si>
+    <t>Fahrradklingel</t>
+  </si>
+  <si>
+    <t>Klingel am Fahrrad, mit der man warnen kann.</t>
+  </si>
+  <si>
+    <t>Fahrradpumpe</t>
+  </si>
+  <si>
+    <t>Pumpe zum Aufblasen von Fahrradreifen.</t>
+  </si>
+  <si>
+    <t>Fernbedienung</t>
+  </si>
+  <si>
+    <t>Handgerät zum Steuern von Fernseher oder anderen Geräten.</t>
+  </si>
+  <si>
+    <t>Feuerlöscher</t>
+  </si>
+  <si>
+    <t>Gerät zum Löschen kleiner Brände.</t>
+  </si>
+  <si>
+    <t>Flaschenöffner</t>
+  </si>
+  <si>
+    <t>Werkzeug zum Öffnen von Flaschen.</t>
+  </si>
+  <si>
+    <t>Flipchart</t>
+  </si>
+  <si>
+    <t>Großer Papierblock auf einem Ständer für Präsentationen.</t>
+  </si>
+  <si>
+    <t>Föhn</t>
+  </si>
+  <si>
+    <t>Elektrisches Gerät zum Trocknen der Haare.</t>
+  </si>
+  <si>
+    <t>Gartenschere</t>
+  </si>
+  <si>
+    <t>Schere zum Schneiden von Pflanzen und Ästen.</t>
+  </si>
+  <si>
+    <t>Gießkanne</t>
+  </si>
+  <si>
+    <t>Behälter mit Tülle zum Bewässern von Pflanzen.</t>
+  </si>
+  <si>
+    <t>Gummistiefel</t>
+  </si>
+  <si>
+    <t>Wasserdichte Stiefel aus Gummi.</t>
+  </si>
+  <si>
+    <t>Handtuchhalter</t>
+  </si>
+  <si>
+    <t>Vorrichtung zum Aufhängen von Handtüchern.</t>
+  </si>
+  <si>
+    <t>Hausnummer</t>
+  </si>
+  <si>
+    <t>Zahl oder Schild, das ein Haus eindeutig kennzeichnet.</t>
+  </si>
+  <si>
+    <t>Heizkörper</t>
+  </si>
+  <si>
+    <t>Gerät, das einen Raum erwärmt.</t>
+  </si>
+  <si>
+    <t>Hängematte</t>
+  </si>
+  <si>
+    <t>Tuch oder Netz zum Liegen, das zwischen zwei Punkten aufgehängt wird.</t>
+  </si>
+  <si>
+    <t>Kabelbinder</t>
+  </si>
+  <si>
+    <t>Kunststoffband zum Bündeln oder Befestigen von Kabeln.</t>
+  </si>
+  <si>
+    <t>Kaffeefilter</t>
+  </si>
+  <si>
+    <t>Filter, durch den Kaffee aufgebrüht wird.</t>
+  </si>
+  <si>
+    <t>Kamerastativ</t>
+  </si>
+  <si>
+    <t>Dreibeiniger Standfuß für eine Kamera.</t>
+  </si>
+  <si>
+    <t>Karaffe</t>
+  </si>
+  <si>
+    <t>Gefäß zum Servieren von Wasser, Wein oder Saft.</t>
+  </si>
+  <si>
+    <t>Kartoffelschäler</t>
+  </si>
+  <si>
+    <t>Küchenwerkzeug zum Schälen von Kartoffeln und Gemüse.</t>
+  </si>
+  <si>
+    <t>Kassenbon</t>
+  </si>
+  <si>
+    <t>Quittung über einen Einkauf.</t>
+  </si>
+  <si>
+    <t>Katzenkorb</t>
+  </si>
+  <si>
+    <t>Transportkorb oder Schlafplatz für eine Katze.</t>
+  </si>
+  <si>
+    <t>Kegelbahn</t>
+  </si>
+  <si>
+    <t>Bahn, auf der Kegeln gespielt wird.</t>
+  </si>
+  <si>
+    <t>Kehrblech</t>
+  </si>
+  <si>
+    <t>Flaches Blech zum Aufnehmen von Schmutz beim Fegen.</t>
+  </si>
+  <si>
+    <t>Klebeband</t>
+  </si>
+  <si>
+    <t>Band mit klebender Oberfläche zum Befestigen.</t>
+  </si>
+  <si>
+    <t>Klettverschluss</t>
+  </si>
+  <si>
+    <t>Verschluss aus Häkchen und Schlaufen.</t>
+  </si>
+  <si>
+    <t>Kochlöffel</t>
+  </si>
+  <si>
+    <t>Langer Löffel zum Umrühren beim Kochen.</t>
+  </si>
+  <si>
+    <t>Kofferraum</t>
+  </si>
+  <si>
+    <t>Stauraum eines Autos für Gepäck.</t>
+  </si>
+  <si>
+    <t>Kompass</t>
+  </si>
+  <si>
+    <t>Instrument zur Bestimmung der Himmelsrichtungen.</t>
+  </si>
+  <si>
+    <t>Kontaktlinse</t>
+  </si>
+  <si>
+    <t>Dünne Linse, die direkt auf dem Auge getragen wird.</t>
+  </si>
+  <si>
+    <t>Korkenzieher</t>
+  </si>
+  <si>
+    <t>Werkzeug zum Herausziehen von Korken.</t>
+  </si>
+  <si>
+    <t>Krawattennadel</t>
+  </si>
+  <si>
+    <t>Schmuckstück oder Clip, der eine Krawatte fixiert.</t>
+  </si>
+  <si>
+    <t>Kugelschreiber</t>
+  </si>
+  <si>
+    <t>Stift mit einer kleinen Kugelspitze und Tinte.</t>
+  </si>
+  <si>
+    <t>Kühlschrankmagnet</t>
+  </si>
+  <si>
+    <t>Magnet, der am Kühlschrank haftet.</t>
+  </si>
+  <si>
+    <t>Ladegerät</t>
+  </si>
+  <si>
+    <t>Gerät zum Aufladen von Akkus.</t>
+  </si>
+  <si>
+    <t>Laminiergerät</t>
+  </si>
+  <si>
+    <t>Gerät, das Papier mit Kunststofffolie versiegelt.</t>
+  </si>
+  <si>
+    <t>Lampenfassung</t>
+  </si>
+  <si>
+    <t>Teil einer Lampe, in den das Leuchtmittel eingesetzt wird.</t>
+  </si>
+  <si>
+    <t>Lattenrost</t>
+  </si>
+  <si>
+    <t>Federnde Unterlage im Bett unter der Matratze.</t>
+  </si>
+  <si>
+    <t>Lautsprecherbox</t>
+  </si>
+  <si>
+    <t>Gehäuse mit Lautsprechern zur Tonwiedergabe.</t>
+  </si>
+  <si>
+    <t>Leiterwagen</t>
+  </si>
+  <si>
+    <t>Kleiner Wagen zum Ziehen, oft für Kinder oder Gepäck.</t>
+  </si>
+  <si>
+    <t>Lesezeichen</t>
+  </si>
+  <si>
+    <t>Markierung, die eine Stelle in einem Buch kennzeichnet.</t>
+  </si>
+  <si>
+    <t>Locher</t>
+  </si>
+  <si>
+    <t>Bürowerkzeug zum Stanzen von Löchern in Papier.</t>
+  </si>
+  <si>
+    <t>Malkasten</t>
+  </si>
+  <si>
+    <t>Kasten mit Wasserfarben zum Malen.</t>
+  </si>
+  <si>
+    <t>Maßband</t>
+  </si>
+  <si>
+    <t>Flexibles Band zum Messen von Längen.</t>
+  </si>
+  <si>
+    <t>Mikrofonständer</t>
+  </si>
+  <si>
+    <t>Ständer, der ein Mikrofon hält.</t>
+  </si>
+  <si>
+    <t>Milchaufschäumer</t>
+  </si>
+  <si>
+    <t>Gerät zum Aufschäumen von Milch.</t>
+  </si>
+  <si>
+    <t>Mülleimerdeckel</t>
+  </si>
+  <si>
+    <t>Deckel eines Behälters für Abfall.</t>
+  </si>
+  <si>
+    <t>Nagelfeile</t>
+  </si>
+  <si>
+    <t>Werkzeug zum Formen und Glätten von Fingernägeln.</t>
+  </si>
+  <si>
+    <t>Nähmaschine</t>
+  </si>
+  <si>
+    <t>Maschine zum Zusammennähen von Stoffen.</t>
+  </si>
+  <si>
+    <t>Notizblock</t>
+  </si>
+  <si>
+    <t>Block mit leeren Seiten für Notizen.</t>
+  </si>
+  <si>
+    <t>Nudelholz</t>
+  </si>
+  <si>
+    <t>Rolle zum Ausrollen von Teig.</t>
+  </si>
+  <si>
+    <t>Ofenhandschuh</t>
+  </si>
+  <si>
+    <t>Dicker Handschuh zum Schutz vor Hitze.</t>
+  </si>
+  <si>
+    <t>Paketband</t>
+  </si>
+  <si>
+    <t>Breites Klebeband zum Verschließen von Paketen.</t>
+  </si>
+  <si>
+    <t>Parkscheibe</t>
+  </si>
+  <si>
+    <t>Scheibe im Auto, mit der die Ankunftszeit angezeigt wird.</t>
+  </si>
+  <si>
+    <t>Pfeffermühle</t>
+  </si>
+  <si>
+    <t>Mühle zum Zerkleinern von Pfefferkörnern.</t>
+  </si>
+  <si>
+    <t>Pflasterspender</t>
+  </si>
+  <si>
+    <t>Behälter, aus dem Pflaster entnommen werden.</t>
+  </si>
+  <si>
+    <t>Pinnwand</t>
+  </si>
+  <si>
+    <t>Tafel, an die Zettel mit Nadeln befestigt werden.</t>
+  </si>
+  <si>
+    <t>Pizzaschneider</t>
+  </si>
+  <si>
+    <t>Rundes Schneidwerkzeug zum Teilen von Pizza.</t>
+  </si>
+  <si>
+    <t>Plattenspieler</t>
+  </si>
+  <si>
+    <t>Gerät zum Abspielen von Schallplatten.</t>
+  </si>
+  <si>
+    <t>Polsterstuhl</t>
+  </si>
+  <si>
+    <t>Gepolsterter Stuhl zum bequemen Sitzen.</t>
+  </si>
+  <si>
+    <t>Pumpe</t>
+  </si>
+  <si>
+    <t>Gerät zum Bewegen von Luft oder Flüssigkeiten.</t>
+  </si>
+  <si>
+    <t>Radiergummi</t>
+  </si>
+  <si>
+    <t>Gummi zum Entfernen von Bleistiftstrichen.</t>
+  </si>
+  <si>
+    <t>Rasierapparat</t>
+  </si>
+  <si>
+    <t>Elektrisches Gerät zum Rasieren.</t>
+  </si>
+  <si>
+    <t>Regenmesser</t>
+  </si>
+  <si>
+    <t>Messgerät für die gefallene Regenmenge.</t>
+  </si>
+  <si>
+    <t>Rollkoffer</t>
+  </si>
+  <si>
+    <t>Koffer mit Rollen und ausziehbarem Griff.</t>
+  </si>
+  <si>
+    <t>Rucksack</t>
+  </si>
+  <si>
+    <t>Tasche, die auf dem Rücken getragen wird.</t>
+  </si>
+  <si>
+    <t>Schneebesen</t>
+  </si>
+  <si>
+    <t>Küchenwerkzeug zum Verquirlen oder Aufschlagen.</t>
+  </si>
+  <si>
+    <t>Schraubstock</t>
+  </si>
+  <si>
+    <t>Werkzeug zum Festspannen von Werkstücken.</t>
+  </si>
+  <si>
+    <t>Schreibtischlampe</t>
+  </si>
+  <si>
+    <t>Lampe für den Arbeitsplatz auf einem Schreibtisch.</t>
+  </si>
+  <si>
+    <t>Schwimmbrille</t>
+  </si>
+  <si>
+    <t>Brille, die beim Schwimmen die Augen schützt.</t>
+  </si>
+  <si>
+    <t>Seifenspender</t>
+  </si>
+  <si>
+    <t>Behälter, der Flüssigseife ausgibt.</t>
+  </si>
+  <si>
+    <t>Sicherheitsnadel</t>
+  </si>
+  <si>
+    <t>Verschließbare Nadel zum Befestigen von Stoff.</t>
+  </si>
+  <si>
+    <t>Sieb</t>
+  </si>
+  <si>
+    <t>Küchengerät zum Abgießen oder Sieben.</t>
+  </si>
+  <si>
+    <t>Sitzsack</t>
+  </si>
+  <si>
+    <t>Weiches Sitzmöbel, das mit kleinen Kügelchen gefüllt ist.</t>
+  </si>
+  <si>
+    <t>Skizzenbuch</t>
+  </si>
+  <si>
+    <t>Buch mit leeren Seiten zum Zeichnen.</t>
+  </si>
+  <si>
+    <t>Sonnenschirmständer</t>
+  </si>
+  <si>
+    <t>Ständer, der einen Sonnenschirm hält.</t>
+  </si>
+  <si>
+    <t>Spardose</t>
+  </si>
+  <si>
+    <t>Behälter zum Sammeln von Münzen.</t>
+  </si>
+  <si>
+    <t>Spiegelreflexkamera</t>
+  </si>
+  <si>
+    <t>Kamera mit Spiegelmechanik und Wechselobjektiven.</t>
+  </si>
+  <si>
+    <t>Spülbürste</t>
+  </si>
+  <si>
+    <t>Bürste zum Reinigen von Geschirr.</t>
+  </si>
+  <si>
+    <t>Standmixer</t>
+  </si>
+  <si>
+    <t>Küchengerät zum Mixen von Zutaten in einem Behälter.</t>
+  </si>
+  <si>
+    <t>Staubsaugerbeutel</t>
+  </si>
+  <si>
+    <t>Beutel im Staubsauger, der Staub sammelt.</t>
+  </si>
+  <si>
+    <t>Steckdosenleiste</t>
+  </si>
+  <si>
+    <t>Mehrfachsteckdose für mehrere elektrische Geräte.</t>
+  </si>
+  <si>
+    <t>Stirnlampe</t>
+  </si>
+  <si>
+    <t>Lampe, die am Kopf getragen wird.</t>
+  </si>
+  <si>
+    <t>Stoppuhr</t>
+  </si>
+  <si>
+    <t>Uhr zum genauen Messen kurzer Zeitintervalle.</t>
+  </si>
+  <si>
+    <t>Tacker</t>
+  </si>
+  <si>
+    <t>Bürowerkzeug zum Heften von Papier mit Klammern.</t>
+  </si>
+  <si>
+    <t>Teekanne</t>
+  </si>
+  <si>
+    <t>Kanne zum Aufbrühen und Servieren von Tee.</t>
+  </si>
+  <si>
+    <t>Thermobecher</t>
+  </si>
+  <si>
+    <t>Becher, der Getränke warm oder kalt hält.</t>
+  </si>
+  <si>
+    <t>Toilettenbürste</t>
+  </si>
+  <si>
+    <t>Bürste zum Reinigen der Toilette.</t>
+  </si>
+  <si>
+    <t>Trinkflasche</t>
+  </si>
+  <si>
+    <t>Wiederverwendbare Flasche zum Trinken unterwegs.</t>
+  </si>
+  <si>
+    <t>Türstopper</t>
+  </si>
+  <si>
+    <t>Gegenstand, der eine Tür offen hält.</t>
+  </si>
+  <si>
+    <t>Überwachungskamera</t>
+  </si>
+  <si>
+    <t>Kamera zur Beobachtung eines Bereichs.</t>
+  </si>
+  <si>
+    <t>Ventilator</t>
+  </si>
+  <si>
+    <t>Gerät, das Luft bewegt und dadurch kühlt.</t>
+  </si>
+  <si>
+    <t>Verlängerungskabel</t>
+  </si>
+  <si>
+    <t>Kabel, das eine Steckdose verlängert.</t>
+  </si>
+  <si>
+    <t>Vorhängeschloss</t>
+  </si>
+  <si>
+    <t>Schloss mit Bügel zum Sichern von Türen oder Ketten.</t>
+  </si>
+  <si>
+    <t>Wäscheklammer</t>
+  </si>
+  <si>
+    <t>Klammer zum Aufhängen von Wäsche.</t>
+  </si>
+  <si>
+    <t>Wasserkocher</t>
+  </si>
+  <si>
+    <t>Gerät zum schnellen Erhitzen von Wasser.</t>
+  </si>
+  <si>
+    <t>Werkzeugkasten</t>
+  </si>
+  <si>
+    <t>Kasten zur Aufbewahrung von Werkzeug.</t>
+  </si>
+  <si>
+    <t>Wetterstation</t>
+  </si>
+  <si>
+    <t>Gerät oder Anlage zur Messung von Wetterdaten.</t>
+  </si>
+  <si>
+    <t>Wok</t>
+  </si>
+  <si>
+    <t>Tiefe runde Pfanne aus der asiatischen Küche.</t>
+  </si>
+  <si>
+    <t>Zahnseide</t>
+  </si>
+  <si>
+    <t>Faden zum Reinigen der Zahnzwischenräume.</t>
+  </si>
+  <si>
+    <t>Zeitschaltuhr</t>
+  </si>
+  <si>
+    <t>Uhr, die Geräte automatisch ein- oder ausschaltet.</t>
+  </si>
+  <si>
+    <t>Altstadtgasse</t>
+  </si>
+  <si>
+    <t>Schmale Straße in einem historischen Stadtviertel.</t>
+  </si>
+  <si>
+    <t>Aussichtsturm</t>
+  </si>
+  <si>
+    <t>Turm, von dem aus man weit über die Umgebung schauen kann.</t>
+  </si>
+  <si>
+    <t>Bahnhofshalle</t>
+  </si>
+  <si>
+    <t>Großer Innenbereich eines Bahnhofs mit Gleisen und Anzeigetafeln.</t>
+  </si>
+  <si>
+    <t>Bergdorf</t>
+  </si>
+  <si>
+    <t>Kleines Dorf in einer Gebirgsregion.</t>
+  </si>
+  <si>
+    <t>Berghütte</t>
+  </si>
+  <si>
+    <t>Einfache Unterkunft in den Bergen für Wanderer und Skifahrer.</t>
+  </si>
+  <si>
+    <t>Bibliothekssaal</t>
+  </si>
+  <si>
+    <t>Raum mit vielen Büchern und Arbeitsplätzen zum Lesen.</t>
+  </si>
+  <si>
+    <t>Botanischer Garten</t>
+  </si>
+  <si>
+    <t>Anlage, in der besondere Pflanzenarten gesammelt und gezeigt werden.</t>
+  </si>
+  <si>
+    <t>Bürogebäude</t>
+  </si>
+  <si>
+    <t>Gebäude mit Arbeitsräumen für Unternehmen oder Behörden.</t>
+  </si>
+  <si>
+    <t>Campingplatz</t>
+  </si>
+  <si>
+    <t>Gelände, auf dem Zelte, Wohnwagen oder Wohnmobile stehen.</t>
+  </si>
+  <si>
+    <t>Dachterrasse</t>
+  </si>
+  <si>
+    <t>Terrasse auf dem Dach eines Gebäudes.</t>
+  </si>
+  <si>
+    <t>Dorfplatz</t>
+  </si>
+  <si>
+    <t>Zentraler Platz in einem Dorf.</t>
+  </si>
+  <si>
+    <t>Einkaufszentrum</t>
+  </si>
+  <si>
+    <t>Großer Gebäudekomplex mit vielen Geschäften.</t>
+  </si>
+  <si>
+    <t>Eishalle</t>
+  </si>
+  <si>
+    <t>Halle mit Eisfläche zum Schlittschuhlaufen oder Eishockeyspielen.</t>
+  </si>
+  <si>
+    <t>Fährhafen</t>
+  </si>
+  <si>
+    <t>Hafen, an dem Fähren anlegen und abfahren.</t>
+  </si>
+  <si>
+    <t>Felsklippe</t>
+  </si>
+  <si>
+    <t>Steile Felswand an Küste oder Berg.</t>
+  </si>
+  <si>
+    <t>Flughafenterminal</t>
+  </si>
+  <si>
+    <t>Gebäude am Flughafen für Check-in, Sicherheitskontrolle und Boarding.</t>
+  </si>
+  <si>
+    <t>Freibad</t>
+  </si>
+  <si>
+    <t>Schwimmbad unter freiem Himmel.</t>
+  </si>
+  <si>
+    <t>Fußgängerzone</t>
+  </si>
+  <si>
+    <t>Straße in der Innenstadt, die hauptsächlich für Fußgänger gedacht ist.</t>
+  </si>
+  <si>
+    <t>Geisterstadt</t>
+  </si>
+  <si>
+    <t>Verlassene Stadt oder Siedlung ohne Bewohner.</t>
+  </si>
+  <si>
+    <t>Gewächshaus</t>
+  </si>
+  <si>
+    <t>Glas- oder Kunststoffbau, in dem Pflanzen geschützt wachsen.</t>
+  </si>
+  <si>
+    <t>Hafenkai</t>
+  </si>
+  <si>
+    <t>Befestigter Uferbereich, an dem Schiffe anlegen.</t>
+  </si>
+  <si>
+    <t>Hörsaal</t>
+  </si>
+  <si>
+    <t>Großer Unterrichtsraum an einer Universität.</t>
+  </si>
+  <si>
+    <t>Hotelrezeption</t>
+  </si>
+  <si>
+    <t>Bereich im Hotel, an dem Gäste ein- und auschecken.</t>
+  </si>
+  <si>
+    <t>Innenhof</t>
+  </si>
+  <si>
+    <t>Offener Hof innerhalb oder zwischen Gebäuden.</t>
+  </si>
+  <si>
+    <t>Jugendherberge</t>
+  </si>
+  <si>
+    <t>Einfache Unterkunft, oft für Gruppen und Reisende.</t>
+  </si>
+  <si>
+    <t>Kletterhalle</t>
+  </si>
+  <si>
+    <t>Halle mit künstlichen Kletterwänden.</t>
+  </si>
+  <si>
+    <t>Konzertsaal</t>
+  </si>
+  <si>
+    <t>Saal, der für Musikaufführungen gebaut ist.</t>
+  </si>
+  <si>
+    <t>Kräutergarten</t>
+  </si>
+  <si>
+    <t>Gartenbereich, in dem Küchen- oder Heilkräuter wachsen.</t>
+  </si>
+  <si>
+    <t>Markthalle</t>
+  </si>
+  <si>
+    <t>Überdachter Ort mit vielen Ständen für Lebensmittel oder Waren.</t>
+  </si>
+  <si>
+    <t>Mensa</t>
+  </si>
+  <si>
+    <t>Kantine an Universität oder Schule.</t>
+  </si>
+  <si>
+    <t>Moorlandschaft</t>
+  </si>
+  <si>
+    <t>Feuchtes Gebiet mit Torfboden und besonderer Vegetation.</t>
+  </si>
+  <si>
+    <t>Opernhaus</t>
+  </si>
+  <si>
+    <t>Theatergebäude für Opernaufführungen.</t>
+  </si>
+  <si>
+    <t>Planetarium</t>
+  </si>
+  <si>
+    <t>Kuppelraum, in dem Sterne und Himmelsbewegungen gezeigt werden.</t>
+  </si>
+  <si>
+    <t>Rathausplatz</t>
+  </si>
+  <si>
+    <t>Platz vor oder neben dem Rathaus einer Stadt.</t>
+  </si>
+  <si>
+    <t>Regenwaldpfad</t>
+  </si>
+  <si>
+    <t>Weg durch dichten tropischen Wald.</t>
+  </si>
+  <si>
+    <t>Reiterhof</t>
+  </si>
+  <si>
+    <t>Hof, auf dem Pferde gehalten und Reitunterricht angeboten wird.</t>
+  </si>
+  <si>
+    <t>Rodelbahn</t>
+  </si>
+  <si>
+    <t>Strecke zum Schlittenfahren.</t>
+  </si>
+  <si>
+    <t>Schlossgarten</t>
+  </si>
+  <si>
+    <t>Gartenanlage bei einem Schloss.</t>
+  </si>
+  <si>
+    <t>Schneehütte</t>
+  </si>
+  <si>
+    <t>Kleine Hütte in verschneiter Umgebung.</t>
+  </si>
+  <si>
+    <t>Schulhof</t>
+  </si>
+  <si>
+    <t>Außenbereich einer Schule für Pausen und Aktivitäten.</t>
+  </si>
+  <si>
+    <t>Segelhafen</t>
+  </si>
+  <si>
+    <t>Hafen für Segelboote und Yachten.</t>
+  </si>
+  <si>
+    <t>Skilift</t>
+  </si>
+  <si>
+    <t>Anlage, die Wintersportler einen Hang hinaufzieht.</t>
+  </si>
+  <si>
+    <t>Stadtmauer</t>
+  </si>
+  <si>
+    <t>Historische Mauer, die früher eine Stadt schützte.</t>
+  </si>
+  <si>
+    <t>Strandpromenade</t>
+  </si>
+  <si>
+    <t>Weg entlang eines Strandes mit Blick auf Meer oder See.</t>
+  </si>
+  <si>
+    <t>Tanzstudio</t>
+  </si>
+  <si>
+    <t>Raum oder Schule für Tanzunterricht.</t>
+  </si>
+  <si>
+    <t>Tiefgarage</t>
+  </si>
+  <si>
+    <t>Unterirdisches Parkhaus.</t>
+  </si>
+  <si>
+    <t>Tropfsteinhöhle</t>
+  </si>
+  <si>
+    <t>Höhle mit Stalaktiten und Stalagmiten aus Kalk.</t>
+  </si>
+  <si>
+    <t>Uferweg</t>
+  </si>
+  <si>
+    <t>Weg entlang eines Flusses, Sees oder Kanals.</t>
+  </si>
+  <si>
+    <t>Universitätscampus</t>
+  </si>
+  <si>
+    <t>Gelände mit Gebäuden einer Hochschule.</t>
+  </si>
+  <si>
+    <t>Vulkaninsel</t>
+  </si>
+  <si>
+    <t>Insel, die durch vulkanische Aktivität entstanden ist.</t>
+  </si>
+  <si>
+    <t>Wartesaal</t>
+  </si>
+  <si>
+    <t>Raum, in dem Menschen vor einer Reise oder einem Termin warten.</t>
+  </si>
+  <si>
+    <t>Wassermühle</t>
+  </si>
+  <si>
+    <t>Mühle, die durch die Kraft fließenden Wassers angetrieben wird.</t>
+  </si>
+  <si>
+    <t>Weinberg</t>
+  </si>
+  <si>
+    <t>Hang oder Feld, auf dem Weinreben wachsen.</t>
+  </si>
+  <si>
+    <t>Windpark</t>
+  </si>
+  <si>
+    <t>Gebiet mit mehreren Windkraftanlagen.</t>
+  </si>
+  <si>
+    <t>Zoogehege</t>
+  </si>
+  <si>
+    <t>Abgetrennter Bereich in einem Zoo für Tiere.</t>
+  </si>
+  <si>
+    <t>Abstimmung</t>
+  </si>
+  <si>
+    <t>Entscheidungsmethode, bei der Stimmen gezählt werden.</t>
+  </si>
+  <si>
+    <t>Achtsamkeit</t>
+  </si>
+  <si>
+    <t>Bewusstes Wahrnehmen des gegenwärtigen Moments.</t>
+  </si>
+  <si>
+    <t>Anarchie</t>
+  </si>
+  <si>
+    <t>Gesellschaftsform ohne zentrale Herrschaft oder Regierung.</t>
+  </si>
+  <si>
+    <t>Antithese</t>
+  </si>
+  <si>
+    <t>Gegenbehauptung oder Gegensatz zu einer These.</t>
+  </si>
+  <si>
+    <t>Arbeitsteilung</t>
+  </si>
+  <si>
+    <t>Aufteilung von Aufgaben auf verschiedene Personen oder Gruppen.</t>
+  </si>
+  <si>
+    <t>Artenvielfalt</t>
+  </si>
+  <si>
+    <t>Vielfalt unterschiedlicher Tier- und Pflanzenarten in einem Gebiet.</t>
+  </si>
+  <si>
+    <t>Aufklärung</t>
+  </si>
+  <si>
+    <t>Epoche und Denkweise, die Vernunft und Bildung betont.</t>
+  </si>
+  <si>
+    <t>Autarkie</t>
+  </si>
+  <si>
+    <t>Zustand, in dem man weitgehend unabhängig von anderen ist.</t>
+  </si>
+  <si>
+    <t>Bauchgefühl</t>
+  </si>
+  <si>
+    <t>Intuitive Einschätzung ohne ausführliche Begründung.</t>
+  </si>
+  <si>
+    <t>Bedingungsloses Grundeinkommen</t>
+  </si>
+  <si>
+    <t>Modell, bei dem jeder regelmäßig Geld vom Staat erhält.</t>
+  </si>
+  <si>
+    <t>Belastungsgrenze</t>
+  </si>
+  <si>
+    <t>Punkt, ab dem etwas oder jemand überfordert ist.</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Vergleichsmaßstab zur Bewertung von Leistung.</t>
+  </si>
+  <si>
+    <t>Beschleunigung</t>
+  </si>
+  <si>
+    <t>Änderung der Geschwindigkeit pro Zeit.</t>
+  </si>
+  <si>
+    <t>Bestäubung</t>
+  </si>
+  <si>
+    <t>Übertragung von Pollen, die bei Pflanzen zur Fortpflanzung führt.</t>
+  </si>
+  <si>
+    <t>Biodiversität</t>
+  </si>
+  <si>
+    <t>Biologische Vielfalt von Genen, Arten und Lebensräumen.</t>
+  </si>
+  <si>
+    <t>Blackout</t>
+  </si>
+  <si>
+    <t>Großflächiger Stromausfall.</t>
+  </si>
+  <si>
+    <t>Brainstorming</t>
+  </si>
+  <si>
+    <t>Kreative Methode zum Sammeln vieler Ideen.</t>
+  </si>
+  <si>
+    <t>Bürokratie</t>
+  </si>
+  <si>
+    <t>Verwaltungssystem mit Regeln, Formularen und Zuständigkeiten.</t>
+  </si>
+  <si>
+    <t>Datenschutz</t>
+  </si>
+  <si>
+    <t>Schutz personenbezogener Daten vor Missbrauch.</t>
+  </si>
+  <si>
+    <t>Deflation</t>
+  </si>
+  <si>
+    <t>Wirtschaftliche Lage, in der das allgemeine Preisniveau sinkt.</t>
+  </si>
+  <si>
+    <t>Demografie</t>
+  </si>
+  <si>
+    <t>Wissenschaftliche Betrachtung von Bevölkerungsstruktur und -entwicklung.</t>
+  </si>
+  <si>
+    <t>Dialektik</t>
+  </si>
+  <si>
+    <t>Methode, bei der Gegensätze diskutiert und weiterentwickelt werden.</t>
+  </si>
+  <si>
+    <t>Dilemma</t>
+  </si>
+  <si>
+    <t>Situation mit zwei schwierigen oder unangenehmen Entscheidungsmöglichkeiten.</t>
+  </si>
+  <si>
+    <t>Dopplereffekt</t>
+  </si>
+  <si>
+    <t>Änderung einer wahrgenommenen Frequenz bei Bewegung von Quelle oder Beobachter.</t>
+  </si>
+  <si>
+    <t>Egoismus</t>
+  </si>
+  <si>
+    <t>Haltung, bei der eigene Interessen stark im Vordergrund stehen.</t>
+  </si>
+  <si>
+    <t>Empathie</t>
+  </si>
+  <si>
+    <t>Fähigkeit, Gefühle anderer Menschen nachzuempfinden.</t>
+  </si>
+  <si>
+    <t>Entropie</t>
+  </si>
+  <si>
+    <t>Maß für Unordnung oder Energieverteilung in einem System.</t>
+  </si>
+  <si>
+    <t>Evolution</t>
+  </si>
+  <si>
+    <t>Langsame Veränderung von Lebewesen über Generationen.</t>
+  </si>
+  <si>
+    <t>Fairness</t>
+  </si>
+  <si>
+    <t>Gerechtes und angemessenes Verhalten gegenüber anderen.</t>
+  </si>
+  <si>
+    <t>Fehlertoleranz</t>
+  </si>
+  <si>
+    <t>Fähigkeit eines Systems, trotz Fehlern weiter zu funktionieren.</t>
+  </si>
+  <si>
+    <t>Feminismus</t>
+  </si>
+  <si>
+    <t>Bewegung für Gleichberechtigung der Geschlechter.</t>
+  </si>
+  <si>
+    <t>Finanzkrise</t>
+  </si>
+  <si>
+    <t>Schwere Störung im Finanzsystem mit wirtschaftlichen Folgen.</t>
+  </si>
+  <si>
+    <t>Föderalismus</t>
+  </si>
+  <si>
+    <t>Staatsprinzip, bei dem Macht zwischen Bund und Ländern verteilt ist.</t>
+  </si>
+  <si>
+    <t>Gedankenexperiment</t>
+  </si>
+  <si>
+    <t>Überlegung, bei der ein hypothetisches Szenario untersucht wird.</t>
+  </si>
+  <si>
+    <t>Gemeinwohl</t>
+  </si>
+  <si>
+    <t>Wohl der Allgemeinheit statt nur einzelner Personen.</t>
+  </si>
+  <si>
+    <t>Gentrifizierung</t>
+  </si>
+  <si>
+    <t>Aufwertung eines Stadtviertels, die oft alte Bewohner verdrängt.</t>
+  </si>
+  <si>
+    <t>Gravitation</t>
+  </si>
+  <si>
+    <t>Anziehungskraft zwischen Massen.</t>
+  </si>
+  <si>
+    <t>Halbwissen</t>
+  </si>
+  <si>
+    <t>Unvollständiges Wissen, das leicht zu falschen Schlussfolgerungen führt.</t>
+  </si>
+  <si>
+    <t>Heimatgefühl</t>
+  </si>
+  <si>
+    <t>Gefühl von Zugehörigkeit zu einem Ort oder Umfeld.</t>
+  </si>
+  <si>
+    <t>Hierarchie</t>
+  </si>
+  <si>
+    <t>Rangordnung mit über- und untergeordneten Ebenen.</t>
+  </si>
+  <si>
+    <t>Hypothese</t>
+  </si>
+  <si>
+    <t>Vorläufige Annahme, die geprüft werden kann.</t>
+  </si>
+  <si>
+    <t>Identität</t>
+  </si>
+  <si>
+    <t>Merkmale und Selbstbild, die eine Person oder Gruppe ausmachen.</t>
+  </si>
+  <si>
+    <t>Ideologie</t>
+  </si>
+  <si>
+    <t>Weltanschauung mit politischen oder gesellschaftlichen Grundannahmen.</t>
+  </si>
+  <si>
+    <t>Immunität</t>
+  </si>
+  <si>
+    <t>Fähigkeit des Körpers, Krankheitserreger abzuwehren.</t>
+  </si>
+  <si>
+    <t>Inflation</t>
+  </si>
+  <si>
+    <t>Anstieg des allgemeinen Preisniveaus.</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>Einführung einer neuen Idee, Technik oder Methode.</t>
+  </si>
+  <si>
+    <t>Instinkt</t>
+  </si>
+  <si>
+    <t>Angeborenes Verhalten ohne bewusstes Lernen.</t>
+  </si>
+  <si>
+    <t>Ironie</t>
+  </si>
+  <si>
+    <t>Aussageform, bei der das Gegenteil des Gemeinten gesagt wird.</t>
+  </si>
+  <si>
+    <t>Kausalität</t>
+  </si>
+  <si>
+    <t>Zusammenhang von Ursache und Wirkung.</t>
+  </si>
+  <si>
+    <t>Kompromiss</t>
+  </si>
+  <si>
+    <t>Einigung, bei der beide Seiten Zugeständnisse machen.</t>
+  </si>
+  <si>
+    <t>Konfliktlösung</t>
+  </si>
+  <si>
+    <t>Prozess zur Beilegung eines Streits.</t>
+  </si>
+  <si>
+    <t>Konsumverhalten</t>
+  </si>
+  <si>
+    <t>Art und Weise, wie Menschen Waren und Dienstleistungen nutzen.</t>
+  </si>
+  <si>
+    <t>Kreislaufwirtschaft</t>
+  </si>
+  <si>
+    <t>Wirtschaftsweise, bei der Ressourcen wiederverwendet werden.</t>
+  </si>
+  <si>
+    <t>Legende</t>
+  </si>
+  <si>
+    <t>Überlieferte Erzählung oder erklärende Beschriftung.</t>
+  </si>
+  <si>
+    <t>Logik</t>
+  </si>
+  <si>
+    <t>Lehre vom folgerichtigen Denken.</t>
+  </si>
+  <si>
+    <t>Mehrwertsteuer</t>
+  </si>
+  <si>
+    <t>Steuer auf den Verkauf von Waren und Dienstleistungen.</t>
+  </si>
+  <si>
+    <t>Metapher</t>
+  </si>
+  <si>
+    <t>Bildhafter Ausdruck, der etwas überträgt beschreibt.</t>
+  </si>
+  <si>
+    <t>Motivation</t>
+  </si>
+  <si>
+    <t>Innerer Antrieb, etwas zu tun.</t>
+  </si>
+  <si>
+    <t>Nachhaltigkeit</t>
+  </si>
+  <si>
+    <t>Handeln, das langfristig Ressourcen schont.</t>
+  </si>
+  <si>
+    <t>Nostalgie</t>
+  </si>
+  <si>
+    <t>Sehnsucht nach einer vergangenen Zeit.</t>
+  </si>
+  <si>
+    <t>Objektivität</t>
+  </si>
+  <si>
+    <t>Sachlichkeit ohne persönliche Verzerrung.</t>
+  </si>
+  <si>
+    <t>Optimismus</t>
+  </si>
+  <si>
+    <t>Zuversichtliche Haltung gegenüber der Zukunft.</t>
+  </si>
+  <si>
+    <t>Paradoxon</t>
+  </si>
+  <si>
+    <t>Aussage oder Situation, die widersprüchlich wirkt.</t>
+  </si>
+  <si>
+    <t>Perspektivwechsel</t>
+  </si>
+  <si>
+    <t>Betrachtung einer Situation aus einem anderen Blickwinkel.</t>
+  </si>
+  <si>
+    <t>Pluralismus</t>
+  </si>
+  <si>
+    <t>Nebeneinander verschiedener Meinungen, Gruppen oder Lebensweisen.</t>
+  </si>
+  <si>
+    <t>Pragmatismus</t>
+  </si>
+  <si>
+    <t>Haltung, die praktische Lösungen in den Vordergrund stellt.</t>
+  </si>
+  <si>
+    <t>Privatsphäre</t>
+  </si>
+  <si>
+    <t>Persönlicher Bereich, der vor Einblicken anderer geschützt ist.</t>
+  </si>
+  <si>
+    <t>Propaganda</t>
+  </si>
+  <si>
+    <t>Gezielte Beeinflussung von Meinungen durch einseitige Informationen.</t>
+  </si>
+  <si>
+    <t>Quarantäne</t>
+  </si>
+  <si>
+    <t>Zeitweilige Absonderung zur Verhinderung von Ansteckung.</t>
+  </si>
+  <si>
+    <t>Recycling</t>
+  </si>
+  <si>
+    <t>Wiederverwertung von Materialien.</t>
+  </si>
+  <si>
+    <t>Redefreiheit</t>
+  </si>
+  <si>
+    <t>Recht, die eigene Meinung frei zu äußern.</t>
+  </si>
+  <si>
+    <t>Relativität</t>
+  </si>
+  <si>
+    <t>Abhängigkeit einer Aussage oder Messung vom Bezugssystem.</t>
+  </si>
+  <si>
+    <t>Resilienz</t>
+  </si>
+  <si>
+    <t>Fähigkeit, Krisen zu überstehen und sich zu erholen.</t>
+  </si>
+  <si>
+    <t>Risikobereitschaft</t>
+  </si>
+  <si>
+    <t>Bereitschaft, unsichere Entscheidungen zu treffen.</t>
+  </si>
+  <si>
+    <t>Satire</t>
+  </si>
+  <si>
+    <t>Spöttische Darstellung zur Kritik an Missständen.</t>
+  </si>
+  <si>
+    <t>Selbstdisziplin</t>
+  </si>
+  <si>
+    <t>Fähigkeit, sich trotz Ablenkung an Ziele zu halten.</t>
+  </si>
+  <si>
+    <t>Solidarität</t>
+  </si>
+  <si>
+    <t>Zusammenhalt und Unterstützung innerhalb einer Gruppe.</t>
+  </si>
+  <si>
+    <t>Stichprobe</t>
+  </si>
+  <si>
+    <t>Auswahl eines Teils, um Rückschlüsse auf eine Gesamtheit zu ziehen.</t>
+  </si>
+  <si>
+    <t>Strategie</t>
+  </si>
+  <si>
+    <t>Langfristiger Plan zur Erreichung eines Ziels.</t>
+  </si>
+  <si>
+    <t>Subvention</t>
+  </si>
+  <si>
+    <t>Finanzielle Unterstützung durch den Staat.</t>
+  </si>
+  <si>
+    <t>Symbolik</t>
+  </si>
+  <si>
+    <t>Bedeutung, die Zeichen, Bilder oder Handlungen tragen.</t>
+  </si>
+  <si>
+    <t>Toleranz</t>
+  </si>
+  <si>
+    <t>Akzeptanz anderer Meinungen oder Lebensweisen.</t>
+  </si>
+  <si>
+    <t>Transparenz</t>
+  </si>
+  <si>
+    <t>Nachvollziehbarkeit und Offenheit von Informationen.</t>
+  </si>
+  <si>
+    <t>Utopie</t>
+  </si>
+  <si>
+    <t>Vorstellung einer idealen, meist unerreichten Gesellschaft.</t>
+  </si>
+  <si>
+    <t>Verhandlung</t>
+  </si>
+  <si>
+    <t>Gespräch, bei dem Parteien eine Einigung suchen.</t>
+  </si>
+  <si>
+    <t>Vertrauen</t>
+  </si>
+  <si>
+    <t>Erwartung, dass jemand zuverlässig oder ehrlich handelt.</t>
+  </si>
+  <si>
+    <t>Vorurteil</t>
+  </si>
+  <si>
+    <t>Vorgefasste Meinung ohne ausreichende Prüfung.</t>
+  </si>
+  <si>
+    <t>Wahrscheinlichkeit</t>
+  </si>
+  <si>
+    <t>Maß dafür, wie wahrscheinlich ein Ereignis ist.</t>
+  </si>
+  <si>
+    <t>Wertschöpfung</t>
+  </si>
+  <si>
+    <t>Entstehung wirtschaftlichen Wertes durch Arbeit oder Produktion.</t>
+  </si>
+  <si>
+    <t>Zensur</t>
+  </si>
+  <si>
+    <t>Kontrolle oder Unterdrückung von Informationen.</t>
+  </si>
+  <si>
+    <t>3D-Drucker</t>
+  </si>
+  <si>
+    <t>Gerät, das dreidimensionale Objekte Schicht für Schicht herstellt.</t>
+  </si>
+  <si>
+    <t>Absorber</t>
+  </si>
+  <si>
+    <t>Bauteil oder Stoff, der Energie oder Strahlung aufnimmt.</t>
+  </si>
+  <si>
+    <t>Adapter</t>
+  </si>
+  <si>
+    <t>Zwischenstück, das unterschiedliche Anschlüsse kompatibel macht.</t>
+  </si>
+  <si>
+    <t>Algorithmisches Denken</t>
+  </si>
+  <si>
+    <t>Problemlösen durch klare Schrittfolgen und Regeln.</t>
+  </si>
+  <si>
+    <t>Antivirusprogramm</t>
+  </si>
+  <si>
+    <t>Software zum Erkennen und Entfernen von Schadprogrammen.</t>
+  </si>
+  <si>
+    <t>App-Store</t>
+  </si>
+  <si>
+    <t>Digitale Plattform zum Herunterladen von Apps.</t>
+  </si>
+  <si>
+    <t>Arduino</t>
+  </si>
+  <si>
+    <t>Kleine Mikrocontroller-Plattform für Elektronikprojekte.</t>
+  </si>
+  <si>
+    <t>Barcode</t>
+  </si>
+  <si>
+    <t>Strichcode zur maschinenlesbaren Kennzeichnung von Produkten.</t>
+  </si>
+  <si>
+    <t>Betriebssystem</t>
+  </si>
+  <si>
+    <t>Grundsoftware, die Hardware und Programme eines Computers verwaltet.</t>
+  </si>
+  <si>
+    <t>Biometrie</t>
+  </si>
+  <si>
+    <t>Erkennung von Personen anhand körperlicher Merkmale.</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>Dezentrale Datenstruktur, die Einträge in Blöcken verkettet.</t>
+  </si>
+  <si>
+    <t>Bluetooth-Lautsprecher</t>
+  </si>
+  <si>
+    <t>Kabelloser Lautsprecher, der über Bluetooth verbunden wird.</t>
+  </si>
+  <si>
+    <t>Botnetz</t>
+  </si>
+  <si>
+    <t>Netzwerk aus infizierten Computern, das ferngesteuert werden kann.</t>
+  </si>
+  <si>
+    <t>Breitbandinternet</t>
+  </si>
+  <si>
+    <t>Schneller Internetzugang mit hoher Datenübertragungsrate.</t>
+  </si>
+  <si>
+    <t>Cloudspeicher</t>
+  </si>
+  <si>
+    <t>Online-Speicherplatz für Dateien auf entfernten Servern.</t>
+  </si>
+  <si>
+    <t>Computerchip</t>
+  </si>
+  <si>
+    <t>Kleines elektronisches Bauteil mit integrierten Schaltungen.</t>
+  </si>
+  <si>
+    <t>Cookie-Banner</t>
+  </si>
+  <si>
+    <t>Hinweis auf Webseiten zur Einwilligung in Cookies.</t>
+  </si>
+  <si>
+    <t>Cyberangriff</t>
+  </si>
+  <si>
+    <t>Digitaler Angriff auf Computersysteme oder Daten.</t>
+  </si>
+  <si>
+    <t>Datenbank</t>
+  </si>
+  <si>
+    <t>Systematische Sammlung von Daten, die gezielt abgefragt werden kann.</t>
+  </si>
+  <si>
+    <t>Datenkabel</t>
+  </si>
+  <si>
+    <t>Kabel zur Übertragung digitaler Informationen.</t>
+  </si>
+  <si>
+    <t>Digitalisierung</t>
+  </si>
+  <si>
+    <t>Umwandlung oder Organisation von Prozessen mit digitaler Technik.</t>
+  </si>
+  <si>
+    <t>Displayglas</t>
+  </si>
+  <si>
+    <t>Glasabdeckung eines Bildschirms.</t>
+  </si>
+  <si>
+    <t>DNA-Sequenz</t>
+  </si>
+  <si>
+    <t>Reihenfolge der Bausteine in einem Abschnitt der Erbinformation.</t>
+  </si>
+  <si>
+    <t>Doppelhelix</t>
+  </si>
+  <si>
+    <t>Spiralige Struktur der DNA aus zwei Strängen.</t>
+  </si>
+  <si>
+    <t>Elektromagnet</t>
+  </si>
+  <si>
+    <t>Magnet, dessen Magnetfeld durch elektrischen Strom entsteht.</t>
+  </si>
+  <si>
+    <t>Elektronenmikroskop</t>
+  </si>
+  <si>
+    <t>Mikroskop, das Elektronen statt Licht verwendet und sehr stark vergrößert.</t>
+  </si>
+  <si>
+    <t>Energiespeicher</t>
+  </si>
+  <si>
+    <t>System, das Energie aufnimmt und später wieder abgibt.</t>
+  </si>
+  <si>
+    <t>Faseroptik</t>
+  </si>
+  <si>
+    <t>Technik zur Datenübertragung mit Licht in Glasfasern.</t>
+  </si>
+  <si>
+    <t>Firewall</t>
+  </si>
+  <si>
+    <t>Schutzsystem, das Netzwerkverkehr kontrolliert.</t>
+  </si>
+  <si>
+    <t>Fitness-Tracker</t>
+  </si>
+  <si>
+    <t>Tragbares Gerät zur Messung von Aktivität, Puls oder Schlaf.</t>
+  </si>
+  <si>
+    <t>Flugsimulator</t>
+  </si>
+  <si>
+    <t>Technisches System zum Üben von Flügen ohne echtes Flugzeug.</t>
+  </si>
+  <si>
+    <t>Frequenzumrichter</t>
+  </si>
+  <si>
+    <t>Gerät, das Frequenz und Spannung für Elektromotoren verändert.</t>
+  </si>
+  <si>
+    <t>Genschnitt</t>
+  </si>
+  <si>
+    <t>Gezielte Veränderung von Erbinformationen.</t>
+  </si>
+  <si>
+    <t>Geothermieanlage</t>
+  </si>
+  <si>
+    <t>Technische Anlage zur Nutzung von Erdwärme.</t>
+  </si>
+  <si>
+    <t>Glasfaserkabel</t>
+  </si>
+  <si>
+    <t>Kabel, das Daten mit Lichtimpulsen überträgt.</t>
+  </si>
+  <si>
+    <t>GPS-Signal</t>
+  </si>
+  <si>
+    <t>Satellitensignal zur Positionsbestimmung.</t>
+  </si>
+  <si>
+    <t>Grafikkarte</t>
+  </si>
+  <si>
+    <t>Computerbauteil zur Berechnung und Ausgabe von Bildern.</t>
+  </si>
+  <si>
+    <t>Halbleiter</t>
+  </si>
+  <si>
+    <t>Material, dessen Leitfähigkeit zwischen Leiter und Isolator liegt.</t>
+  </si>
+  <si>
+    <t>Hologramm</t>
+  </si>
+  <si>
+    <t>Dreidimensionale Lichtdarstellung eines Objekts.</t>
+  </si>
+  <si>
+    <t>Hybridauto</t>
+  </si>
+  <si>
+    <t>Auto mit Verbrennungs- und Elektromotor.</t>
+  </si>
+  <si>
+    <t>Infrarotkamera</t>
+  </si>
+  <si>
+    <t>Kamera, die Wärmestrahlung sichtbar machen kann.</t>
+  </si>
+  <si>
+    <t>Internetrouter</t>
+  </si>
+  <si>
+    <t>Gerät, das ein Heimnetzwerk mit dem Internet verbindet.</t>
+  </si>
+  <si>
+    <t>Joystick</t>
+  </si>
+  <si>
+    <t>Eingabegerät zur Steuerung von Spielen oder Maschinen.</t>
+  </si>
+  <si>
+    <t>Kernfusion</t>
+  </si>
+  <si>
+    <t>Verschmelzung leichter Atomkerne unter Freisetzung von Energie.</t>
+  </si>
+  <si>
+    <t>Klimamodell</t>
+  </si>
+  <si>
+    <t>Computermodell zur Simulation des Klimas.</t>
+  </si>
+  <si>
+    <t>Kompressionsalgorithmus</t>
+  </si>
+  <si>
+    <t>Verfahren zur Verringerung der Datenmenge.</t>
+  </si>
+  <si>
+    <t>Kryptografie</t>
+  </si>
+  <si>
+    <t>Wissenschaft der Verschlüsselung und sicheren Kommunikation.</t>
+  </si>
+  <si>
+    <t>Ladestation</t>
+  </si>
+  <si>
+    <t>Ort oder Gerät zum Aufladen von Elektrofahrzeugen oder Akkus.</t>
+  </si>
+  <si>
+    <t>Laserpointer</t>
+  </si>
+  <si>
+    <t>Kleines Gerät, das einen gebündelten Lichtstrahl erzeugt.</t>
+  </si>
+  <si>
+    <t>LiDAR</t>
+  </si>
+  <si>
+    <t>Messverfahren, das Entfernungen mit Laserlicht bestimmt.</t>
+  </si>
+  <si>
+    <t>Lithium-Ionen-Akku</t>
+  </si>
+  <si>
+    <t>Wiederaufladbarer Akku, der häufig in Elektronik und E-Autos steckt.</t>
+  </si>
+  <si>
+    <t>Mikrochip</t>
+  </si>
+  <si>
+    <t>Sehr kleiner Chip mit elektronischen Schaltungen.</t>
+  </si>
+  <si>
+    <t>Mikroplastik</t>
+  </si>
+  <si>
+    <t>Winzige Kunststoffteilchen in Umwelt und Produkten.</t>
+  </si>
+  <si>
+    <t>Nanotechnologie</t>
+  </si>
+  <si>
+    <t>Technik im Bereich extrem kleiner Strukturen.</t>
+  </si>
+  <si>
+    <t>Netzteil</t>
+  </si>
+  <si>
+    <t>Gerät, das elektrische Spannung für ein Gerät bereitstellt.</t>
+  </si>
+  <si>
+    <t>Neuralnetz</t>
+  </si>
+  <si>
+    <t>Computermodell, das lose an Nervennetze angelehnt ist.</t>
+  </si>
+  <si>
+    <t>Passwortmanager</t>
+  </si>
+  <si>
+    <t>Programm zum Speichern und Erzeugen sicherer Passwörter.</t>
+  </si>
+  <si>
+    <t>Photovoltaikanlage</t>
+  </si>
+  <si>
+    <t>Anlage, die Sonnenlicht direkt in elektrischen Strom umwandelt.</t>
+  </si>
+  <si>
+    <t>Podcast-App</t>
+  </si>
+  <si>
+    <t>Programm zum Abspielen und Verwalten von Podcasts.</t>
+  </si>
+  <si>
+    <t>Prototyp</t>
+  </si>
+  <si>
+    <t>Erstes Modell eines Produkts oder Systems zum Testen.</t>
+  </si>
+  <si>
+    <t>Quantencomputer</t>
+  </si>
+  <si>
+    <t>Rechner, der quantenmechanische Effekte für Berechnungen nutzt.</t>
+  </si>
+  <si>
+    <t>QR-Code</t>
+  </si>
+  <si>
+    <t>Zweidimensionaler Code, der mit Kameras gelesen werden kann.</t>
+  </si>
+  <si>
+    <t>Raketenantrieb</t>
+  </si>
+  <si>
+    <t>Antrieb, der Rückstoß aus ausgestoßenen Gasen nutzt.</t>
+  </si>
+  <si>
+    <t>Rechenzentrum</t>
+  </si>
+  <si>
+    <t>Gebäude mit vielen Servern und Netzwerktechnik.</t>
+  </si>
+  <si>
+    <t>Roboterarm</t>
+  </si>
+  <si>
+    <t>Mechanischer Arm, der Bewegungen automatisch ausführen kann.</t>
+  </si>
+  <si>
+    <t>Satellitenschüssel</t>
+  </si>
+  <si>
+    <t>Antenne zum Empfang von Signalen von Satelliten.</t>
+  </si>
+  <si>
+    <t>Schaltkreis</t>
+  </si>
+  <si>
+    <t>Verbindung elektrischer Bauteile, durch die Strom fließen kann.</t>
+  </si>
+  <si>
+    <t>Sensorik</t>
+  </si>
+  <si>
+    <t>Technik zur Erfassung physikalischer oder chemischer Größen.</t>
+  </si>
+  <si>
+    <t>Serverraum</t>
+  </si>
+  <si>
+    <t>Raum, in dem Server und Netzwerktechnik stehen.</t>
+  </si>
+  <si>
+    <t>Solarthermie</t>
+  </si>
+  <si>
+    <t>Nutzung von Sonnenwärme zur Erwärmung von Wasser oder Räumen.</t>
+  </si>
+  <si>
+    <t>Sprachassistent</t>
+  </si>
+  <si>
+    <t>Software, die Sprachbefehle versteht und darauf reagiert.</t>
+  </si>
+  <si>
+    <t>Streamingdienst</t>
+  </si>
+  <si>
+    <t>Online-Dienst zum Abspielen von Musik oder Videos.</t>
+  </si>
+  <si>
+    <t>Teleskoplinse</t>
+  </si>
+  <si>
+    <t>Optisches Bauteil, das Licht in einem Teleskop bündelt.</t>
+  </si>
+  <si>
+    <t>Touchscreen</t>
+  </si>
+  <si>
+    <t>Bildschirm, der Berührungen als Eingaben erkennt.</t>
+  </si>
+  <si>
+    <t>Ultraschall</t>
+  </si>
+  <si>
+    <t>Schall mit Frequenzen oberhalb des menschlichen Hörbereichs.</t>
+  </si>
+  <si>
+    <t>USB-C-Kabel</t>
+  </si>
+  <si>
+    <t>Kabel mit modernem, beidseitig einsteckbarem USB-Stecker.</t>
+  </si>
+  <si>
+    <t>Virtual Reality</t>
+  </si>
+  <si>
+    <t>Computergenerierte Umgebung, die über eine Brille erlebt wird.</t>
+  </si>
+  <si>
+    <t>Wärmepumpe</t>
+  </si>
+  <si>
+    <t>Technisches Gerät, das Wärme von einem niedrigeren auf ein höheres Temperaturniveau bringt.</t>
+  </si>
+  <si>
+    <t>Wearable</t>
+  </si>
+  <si>
+    <t>Tragbares elektronisches Gerät, zum Beispiel Smartwatch oder Fitnessband.</t>
+  </si>
+  <si>
+    <t>Webcam</t>
+  </si>
+  <si>
+    <t>Kamera für Videoübertragungen am Computer.</t>
+  </si>
+  <si>
+    <t>Windturbine</t>
+  </si>
+  <si>
+    <t>Maschine, die Windenergie in Drehbewegung umwandelt.</t>
+  </si>
+  <si>
+    <t>Der Hobbit</t>
+  </si>
+  <si>
+    <t>Fantasyroman von J. R. R. Tolkien über Bilbo Beutlins Reise zum Einsamen Berg.</t>
+  </si>
+  <si>
+    <t>Dracula</t>
+  </si>
+  <si>
+    <t>Romanfigur und berühmter Vampir aus Bram Stokers gleichnamigem Buch.</t>
+  </si>
+  <si>
+    <t>Moby-Dick</t>
+  </si>
+  <si>
+    <t>Roman über die Jagd des Kapitän Ahab auf einen weißen Wal.</t>
+  </si>
+  <si>
+    <t>Robinson Crusoe</t>
+  </si>
+  <si>
+    <t>Abenteuerroman über einen Schiffbrüchigen auf einer einsamen Insel.</t>
+  </si>
+  <si>
+    <t>Alice im Wunderland</t>
+  </si>
+  <si>
+    <t>Fantastische Geschichte über ein Mädchen in einer absurden Traumwelt.</t>
+  </si>
+  <si>
+    <t>Peter Pan</t>
+  </si>
+  <si>
+    <t>Fiktiver Junge, der nicht erwachsen wird und in Nimmerland lebt.</t>
+  </si>
+  <si>
+    <t>Winnetou</t>
+  </si>
+  <si>
+    <t>Fiktiver Apachenhäuptling aus den Romanen von Karl May.</t>
+  </si>
+  <si>
+    <t>Pippi Langstrumpf</t>
+  </si>
+  <si>
+    <t>Kinderbuchfigur mit roten Zöpfen, großem Mut und übermenschlicher Kraft.</t>
+  </si>
+  <si>
+    <t>Momo</t>
+  </si>
+  <si>
+    <t>Romanfigur von Michael Ende, die gegen die grauen Herren kämpft.</t>
+  </si>
+  <si>
+    <t>Die unendliche Geschichte</t>
+  </si>
+  <si>
+    <t>Fantasyroman von Michael Ende über Bastian und das Land Phantásien.</t>
+  </si>
+  <si>
+    <t>Krabat</t>
+  </si>
+  <si>
+    <t>Roman über einen Jungen in einer geheimnisvollen Mühle und schwarze Magie.</t>
+  </si>
+  <si>
+    <t>Tintenherz</t>
+  </si>
+  <si>
+    <t>Fantasyroman, in dem Figuren aus Büchern in die reale Welt gelangen.</t>
+  </si>
+  <si>
+    <t>Die drei Fragezeichen</t>
+  </si>
+  <si>
+    <t>Jugendbuch- und Hörspielreihe über drei Detektive aus Rocky Beach.</t>
+  </si>
+  <si>
+    <t>Fünf Freunde</t>
+  </si>
+  <si>
+    <t>Kinderbuchreihe über vier Kinder und einen Hund, die Abenteuer erleben.</t>
+  </si>
+  <si>
+    <t>Hamlet</t>
+  </si>
+  <si>
+    <t>Shakespeares Tragödie über einen dänischen Prinzen und Rache.</t>
+  </si>
+  <si>
+    <t>Macbeth</t>
+  </si>
+  <si>
+    <t>Shakespeares Tragödie über Machtgier und Schuld.</t>
+  </si>
+  <si>
+    <t>Odyssee</t>
+  </si>
+  <si>
+    <t>Antikes Epos über die Irrfahrten des Odysseus.</t>
+  </si>
+  <si>
+    <t>Ilias</t>
+  </si>
+  <si>
+    <t>Antikes Epos über Ereignisse des Trojanischen Kriegs.</t>
+  </si>
+  <si>
+    <t>Nibelungenlied</t>
+  </si>
+  <si>
+    <t>Mittelalterliches Heldenepos über Siegfried, Kriemhild und Rache.</t>
+  </si>
+  <si>
+    <t>Citizen Kane</t>
+  </si>
+  <si>
+    <t>Einflussreicher Film über Aufstieg und Einsamkeit eines Medienmagnaten.</t>
+  </si>
+  <si>
+    <t>Inception</t>
+  </si>
+  <si>
+    <t>Film über Träume in Träumen und das Manipulieren von Erinnerungen.</t>
+  </si>
+  <si>
+    <t>Interstellar</t>
+  </si>
+  <si>
+    <t>Science-Fiction-Film über Raumfahrt, Zeitdilatation und die Suche nach einer neuen Heimat.</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>Science-Fiction-Film über den Mond Pandora und die Na'vi.</t>
+  </si>
+  <si>
+    <t>Gladiator</t>
+  </si>
+  <si>
+    <t>Historienfilm über einen römischen Feldherrn, der zum Gladiator wird.</t>
+  </si>
+  <si>
+    <t>Der König der Löwen</t>
+  </si>
+  <si>
+    <t>Disneyfilm über den jungen Löwen Simba.</t>
+  </si>
+  <si>
+    <t>Findet Nemo</t>
+  </si>
+  <si>
+    <t>Animationsfilm über einen Clownfisch, der seinen Sohn sucht.</t>
+  </si>
+  <si>
+    <t>Toy Story</t>
+  </si>
+  <si>
+    <t>Animationsfilm über Spielzeuge, die heimlich lebendig sind.</t>
+  </si>
+  <si>
+    <t>Shrek</t>
+  </si>
+  <si>
+    <t>Animationsfilm, der Märchen humorvoll auf den Kopf stellt.</t>
+  </si>
+  <si>
+    <t>Ice Age</t>
+  </si>
+  <si>
+    <t>Animationsfilmreihe über Tiere in der Eiszeit.</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Animationsfilm über einen kleinen Müllroboter auf der Erde.</t>
+  </si>
+  <si>
+    <t>Ratatouille</t>
+  </si>
+  <si>
+    <t>Animationsfilm über eine kochende Ratte in Paris.</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>Animationsfilm über Familie, Musik und den Tag der Toten.</t>
+  </si>
+  <si>
+    <t>Die Eiskönigin</t>
+  </si>
+  <si>
+    <t>Disneyfilm über die Schwestern Elsa und Anna.</t>
+  </si>
+  <si>
+    <t>Kung Fu Panda</t>
+  </si>
+  <si>
+    <t>Animationsfilm über einen Panda, der Kung-Fu-Meister wird.</t>
+  </si>
+  <si>
+    <t>Drachenzähmen leicht gemacht</t>
+  </si>
+  <si>
+    <t>Animationsfilm über Wikinger und Drachen.</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
+    <t>Animationsfilm über Zootiere, die in der Wildnis landen.</t>
+  </si>
+  <si>
+    <t>Minions</t>
+  </si>
+  <si>
+    <t>Gelbe Figuren aus der Filmreihe „Ich – Einfach unverbesserlich“.</t>
+  </si>
+  <si>
+    <t>Obelix</t>
+  </si>
+  <si>
+    <t>Comicfigur aus Asterix, bekannt für Stärke und Hinkelsteine.</t>
+  </si>
+  <si>
+    <t>Lucky Luke</t>
+  </si>
+  <si>
+    <t>Comic-Cowboy, der schneller schießt als sein Schatten.</t>
+  </si>
+  <si>
+    <t>Tim und Struppi</t>
+  </si>
+  <si>
+    <t>Comicreihe über einen Reporter und seinen Hund.</t>
+  </si>
+  <si>
+    <t>Donald Duck</t>
+  </si>
+  <si>
+    <t>Disney-Ente, bekannt für Pech und Wutausbrüche.</t>
+  </si>
+  <si>
+    <t>Mickey Maus</t>
+  </si>
+  <si>
+    <t>Berühmte Disney-Maus und Symbolfigur des Unternehmens.</t>
+  </si>
+  <si>
+    <t>Dagobert Duck</t>
+  </si>
+  <si>
+    <t>Reicher Entenhausener mit Geldspeicher.</t>
+  </si>
+  <si>
+    <t>Garfield</t>
+  </si>
+  <si>
+    <t>Fauler orangefarbener Comic-Kater, der Lasagne liebt.</t>
+  </si>
+  <si>
+    <t>Snoopy</t>
+  </si>
+  <si>
+    <t>Hund aus den Peanuts-Comics, der auf seiner Hundehütte liegt.</t>
+  </si>
+  <si>
+    <t>Calvin und Hobbes</t>
+  </si>
+  <si>
+    <t>Comic über einen Jungen und seinen Stofftiger.</t>
+  </si>
+  <si>
+    <t>Superman</t>
+  </si>
+  <si>
+    <t>Superheld vom Planeten Krypton mit übermenschlichen Kräften.</t>
+  </si>
+  <si>
+    <t>Wonder Woman</t>
+  </si>
+  <si>
+    <t>Superheldin mit Lasso der Wahrheit und amazonischer Herkunft.</t>
+  </si>
+  <si>
+    <t>Iron Man</t>
+  </si>
+  <si>
+    <t>Superheld in technischer Rüstung, auch Tony Stark genannt.</t>
+  </si>
+  <si>
+    <t>Captain America</t>
+  </si>
+  <si>
+    <t>Superheld mit Schild und patriotischem Kostüm.</t>
+  </si>
+  <si>
+    <t>Hulk</t>
+  </si>
+  <si>
+    <t>Grüner Superheld, der bei Wut riesig und stark wird.</t>
+  </si>
+  <si>
+    <t>Thor</t>
+  </si>
+  <si>
+    <t>Marvel-Superheld und Donnergott mit Hammer.</t>
+  </si>
+  <si>
+    <t>Black Panther</t>
+  </si>
+  <si>
+    <t>Superheld und König des fiktiven Staates Wakanda.</t>
+  </si>
+  <si>
+    <t>Aquaman</t>
+  </si>
+  <si>
+    <t>Superheld, der mit Meereswesen kommunizieren kann.</t>
+  </si>
+  <si>
+    <t>Joker</t>
+  </si>
+  <si>
+    <t>Comic-Bösewicht und Gegenspieler von Batman.</t>
+  </si>
+  <si>
+    <t>Yoda</t>
+  </si>
+  <si>
+    <t>Weiser Jedi-Meister aus Star Wars.</t>
+  </si>
+  <si>
+    <t>Chewbacca</t>
+  </si>
+  <si>
+    <t>Wookiee und Co-Pilot des Millennium Falcon.</t>
+  </si>
+  <si>
+    <t>R2-D2</t>
+  </si>
+  <si>
+    <t>Kleiner Astromech-Droide aus Star Wars.</t>
+  </si>
+  <si>
+    <t>C-3PO</t>
+  </si>
+  <si>
+    <t>Goldfarbener Protokolldroide aus Star Wars.</t>
+  </si>
+  <si>
+    <t>Leia Organa</t>
+  </si>
+  <si>
+    <t>Prinzessin und Widerstandsanführerin aus Star Wars.</t>
+  </si>
+  <si>
+    <t>Luke Skywalker</t>
+  </si>
+  <si>
+    <t>Jedi-Held aus Star Wars.</t>
+  </si>
+  <si>
+    <t>Frodo Beutlin</t>
+  </si>
+  <si>
+    <t>Hobbit, der den Einen Ring nach Mordor trägt.</t>
+  </si>
+  <si>
+    <t>Aragorn</t>
+  </si>
+  <si>
+    <t>Waldläufer und Königserbe aus Der Herr der Ringe.</t>
+  </si>
+  <si>
+    <t>Legolas</t>
+  </si>
+  <si>
+    <t>Elbischer Bogenschütze aus Der Herr der Ringe.</t>
+  </si>
+  <si>
+    <t>Hermine Granger</t>
+  </si>
+  <si>
+    <t>Sehr kluge Hexe aus der Harry-Potter-Reihe.</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Bester Freund von Harry Potter aus der Zaubererfamilie Weasley.</t>
+  </si>
+  <si>
+    <t>Albus Dumbledore</t>
+  </si>
+  <si>
+    <t>Schulleiter von Hogwarts und mächtiger Zauberer.</t>
+  </si>
+  <si>
+    <t>Severus Snape</t>
+  </si>
+  <si>
+    <t>Zaubertranklehrer aus Harry Potter mit geheimnisvoller Rolle.</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Dunkler Zauberer und Hauptgegner von Harry Potter.</t>
+  </si>
+  <si>
+    <t>Hagrid</t>
+  </si>
+  <si>
+    <t>Halbriese und Wildhüter von Hogwarts.</t>
+  </si>
+  <si>
+    <t>Sauron</t>
+  </si>
+  <si>
+    <t>Dunkler Herrscher aus Der Herr der Ringe.</t>
+  </si>
+  <si>
+    <t>Bilbo Beutlin</t>
+  </si>
+  <si>
+    <t>Hobbit, der den Ring findet und ein Abenteuer erlebt.</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Heldin aus Die Tribute von Panem mit Pfeil und Bogen.</t>
+  </si>
+  <si>
+    <t>Indiana Jones</t>
+  </si>
+  <si>
+    <t>Abenteuerarchäologe mit Hut und Peitsche.</t>
+  </si>
+  <si>
+    <t>James Bond</t>
+  </si>
+  <si>
+    <t>Britischer Geheimagent mit der Kennnummer 007.</t>
+  </si>
+  <si>
+    <t>Rocky Balboa</t>
+  </si>
+  <si>
+    <t>Fiktiver Boxer aus der Rocky-Filmreihe.</t>
+  </si>
+  <si>
+    <t>Mary Poppins</t>
+  </si>
+  <si>
+    <t>Magisches Kindermädchen mit Regenschirm.</t>
+  </si>
+  <si>
+    <t>Gargamel</t>
+  </si>
+  <si>
+    <t>Zauberer und Gegenspieler der Schlümpfe.</t>
+  </si>
+  <si>
+    <t>Papa Schlumpf</t>
+  </si>
+  <si>
+    <t>Bärtiger Anführer der Schlümpfe.</t>
+  </si>
+  <si>
+    <t>Bibi Blocksberg</t>
+  </si>
+  <si>
+    <t>Junge Hexe aus deutschen Hörspielen und Büchern.</t>
+  </si>
+  <si>
+    <t>Benjamin Blümchen</t>
+  </si>
+  <si>
+    <t>Sprechender Elefant aus deutschen Kinderhörspielen.</t>
+  </si>
+  <si>
+    <t>Käpt'n Blaubär</t>
+  </si>
+  <si>
+    <t>Seemannsbär, der erfundene Geschichten erzählt.</t>
+  </si>
+  <si>
+    <t>Sandmännchen</t>
+  </si>
+  <si>
+    <t>Fernsehfigur, die Kindern eine Gute-Nacht-Geschichte bringt.</t>
+  </si>
+  <si>
+    <t>Bernd das Brot</t>
+  </si>
+  <si>
+    <t>Mürrische sprechende Brotfigur aus dem Kinderkanal.</t>
+  </si>
+  <si>
+    <t>Bogenschießen</t>
+  </si>
+  <si>
+    <t>Sportart, bei der Pfeile mit einem Bogen auf eine Zielscheibe geschossen werden.</t>
+  </si>
+  <si>
+    <t>Bouldern</t>
+  </si>
+  <si>
+    <t>Klettern in Absprunghöhe ohne Seil, meist an künstlichen Wänden.</t>
+  </si>
+  <si>
+    <t>Curling</t>
+  </si>
+  <si>
+    <t>Eissportart, bei der Steine über das Eis geschoben und mit Besen gelenkt werden.</t>
+  </si>
+  <si>
+    <t>Dreisprung</t>
+  </si>
+  <si>
+    <t>Leichtathletikdisziplin mit Hop, Step und Jump.</t>
+  </si>
+  <si>
+    <t>Fechten</t>
+  </si>
+  <si>
+    <t>Kampfsport mit Degen, Florett oder Säbel.</t>
+  </si>
+  <si>
+    <t>Frisbee</t>
+  </si>
+  <si>
+    <t>Wurfscheibe und Spiel, bei dem die Scheibe gefangen wird.</t>
+  </si>
+  <si>
+    <t>Geocaching</t>
+  </si>
+  <si>
+    <t>Moderne Schatzsuche mit GPS-Koordinaten.</t>
+  </si>
+  <si>
+    <t>Gewichtheben</t>
+  </si>
+  <si>
+    <t>Sportart, bei der schwere Hanteln über den Kopf gehoben werden.</t>
+  </si>
+  <si>
+    <t>Hochsprung</t>
+  </si>
+  <si>
+    <t>Leichtathletikdisziplin, bei der eine Latte übersprungen wird.</t>
+  </si>
+  <si>
+    <t>Kampfsport</t>
+  </si>
+  <si>
+    <t>Sammelbegriff für sportliche Zweikämpfe mit Regeln.</t>
+  </si>
+  <si>
+    <t>Kitesurfen</t>
+  </si>
+  <si>
+    <t>Wassersport, bei dem ein Board mit einem Lenkdrachen gezogen wird.</t>
+  </si>
+  <si>
+    <t>Langlauf</t>
+  </si>
+  <si>
+    <t>Wintersportart mit Skiern auf langen Strecken.</t>
+  </si>
+  <si>
+    <t>Minigolf</t>
+  </si>
+  <si>
+    <t>Geschicklichkeitsspiel auf kleinen Bahnen mit Hindernissen.</t>
+  </si>
+  <si>
+    <t>Parkour</t>
+  </si>
+  <si>
+    <t>Bewegungskunst, bei der Hindernisse effizient überwunden werden.</t>
+  </si>
+  <si>
+    <t>Rudern</t>
+  </si>
+  <si>
+    <t>Wassersport, bei dem ein Boot mit Rudern bewegt wird.</t>
+  </si>
+  <si>
+    <t>Slackline</t>
+  </si>
+  <si>
+    <t>Balancieren auf einem gespannten Band.</t>
+  </si>
+  <si>
+    <t>Snowboarden</t>
+  </si>
+  <si>
+    <t>Wintersport auf einem breiten Brett im Schnee.</t>
+  </si>
+  <si>
+    <t>Speerwurf</t>
+  </si>
+  <si>
+    <t>Leichtathletikdisziplin, bei der ein Speer möglichst weit geworfen wird.</t>
+  </si>
+  <si>
+    <t>Stand-up-Paddling</t>
+  </si>
+  <si>
+    <t>Wassersport, bei dem man stehend auf einem Board paddelt.</t>
+  </si>
+  <si>
+    <t>Tischkicker</t>
+  </si>
+  <si>
+    <t>Spiel mit drehbaren Stangen und kleinen Fußballfiguren.</t>
+  </si>
+  <si>
+    <t>Trampolinspringen</t>
+  </si>
+  <si>
+    <t>Sportart mit Sprüngen auf einem elastischen Tuch.</t>
+  </si>
+  <si>
+    <t>Triathlon</t>
+  </si>
+  <si>
+    <t>Ausdauersport aus Schwimmen, Radfahren und Laufen.</t>
+  </si>
+  <si>
+    <t>Ultimate Frisbee</t>
+  </si>
+  <si>
+    <t>Teamsport mit Frisbee-Scheibe und Endzonen.</t>
+  </si>
+  <si>
+    <t>Wasserball</t>
+  </si>
+  <si>
+    <t>Mannschaftssport im Wasser mit Toren.</t>
+  </si>
+  <si>
+    <t>Zehnkampf</t>
+  </si>
+  <si>
+    <t>Leichtathletikwettbewerb aus zehn Disziplinen.</t>
+  </si>
+  <si>
+    <t>Yoga-Matte</t>
+  </si>
+  <si>
+    <t>Unterlage für Yogaübungen.</t>
+  </si>
+  <si>
+    <t>Boxsack</t>
+  </si>
+  <si>
+    <t>Gefüllter Sack zum Trainieren von Schlägen.</t>
+  </si>
+  <si>
+    <t>Startblock</t>
+  </si>
+  <si>
+    <t>Hilfsmittel für Sprinter beim Start.</t>
+  </si>
+  <si>
+    <t>Torwartparade</t>
+  </si>
+  <si>
+    <t>Abwehraktion eines Torwarts.</t>
+  </si>
+  <si>
+    <t>Elfmeterpunkt</t>
+  </si>
+  <si>
+    <t>Markierung im Fußball, von der Strafstöße geschossen werden.</t>
+  </si>
+  <si>
+    <t>Freistoßmauer</t>
+  </si>
+  <si>
+    <t>Spielerreihe, die beim Fußball einen Freistoß blocken soll.</t>
+  </si>
+  <si>
+    <t>Eckfahne</t>
+  </si>
+  <si>
+    <t>Fahne an der Ecke eines Fußballfelds.</t>
+  </si>
+  <si>
+    <t>Abseitsfalle</t>
+  </si>
+  <si>
+    <t>Taktik im Fußball, um Gegner ins Abseits zu stellen.</t>
+  </si>
+  <si>
+    <t>Zeitspiel</t>
+  </si>
+  <si>
+    <t>Verzögern eines Spiels, um einen Vorsprung zu sichern.</t>
+  </si>
+  <si>
+    <t>Foto-Finish</t>
+  </si>
+  <si>
+    <t>Zielfoto zur Entscheidung eines knappen Rennens.</t>
+  </si>
+  <si>
+    <t>Siegerpodest</t>
+  </si>
+  <si>
+    <t>Podest, auf dem die besten Sportler geehrt werden.</t>
+  </si>
+  <si>
+    <t>La-Ola-Welle</t>
+  </si>
+  <si>
+    <t>Wellenförmiges Aufstehen des Publikums im Stadion.</t>
+  </si>
+  <si>
+    <t>Maskottchen</t>
+  </si>
+  <si>
+    <t>Glücks- oder Werbefigur eines Teams oder Events.</t>
+  </si>
+  <si>
+    <t>Fanblock</t>
+  </si>
+  <si>
+    <t>Bereich im Stadion mit besonders aktiven Anhängern.</t>
+  </si>
+  <si>
+    <t>Sportkommentator</t>
+  </si>
+  <si>
+    <t>Person, die ein Sportereignis live erklärt.</t>
+  </si>
+  <si>
+    <t>Halbzeitpause</t>
+  </si>
+  <si>
+    <t>Pause zwischen zwei Spielhälften.</t>
+  </si>
+  <si>
+    <t>Nachspielzeit</t>
+  </si>
+  <si>
+    <t>Zusätzliche Spielzeit am Ende einer Halbzeit.</t>
+  </si>
+  <si>
+    <t>Pokalübergabe</t>
+  </si>
+  <si>
+    <t>Moment, in dem der Sieger einen Pokal erhält.</t>
+  </si>
+  <si>
+    <t>Trainingslager</t>
+  </si>
+  <si>
+    <t>Ort und Zeit intensiver Vorbereitung einer Mannschaft.</t>
+  </si>
+  <si>
+    <t>Mannschaftskapitän</t>
+  </si>
+  <si>
+    <t>Spieler, der ein Team offiziell führt.</t>
+  </si>
+  <si>
+    <t>Schiedsrichterpfiff</t>
+  </si>
+  <si>
+    <t>Pfiff, mit dem ein Schiedsrichter das Spiel lenkt.</t>
+  </si>
+  <si>
+    <t>Videobeweis</t>
+  </si>
+  <si>
+    <t>Technische Überprüfung strittiger Spielszenen.</t>
+  </si>
+  <si>
+    <t>Dopingkontrolle</t>
+  </si>
+  <si>
+    <t>Test, ob verbotene leistungssteigernde Mittel genutzt wurden.</t>
+  </si>
+  <si>
+    <t>Startnummer</t>
+  </si>
+  <si>
+    <t>Nummer, mit der Sportler im Wettkampf identifiziert werden.</t>
+  </si>
+  <si>
+    <t>Zielgerade</t>
+  </si>
+  <si>
+    <t>Letzter gerader Abschnitt vor dem Ziel.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4569,16 +8547,27 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4586,19 +8575,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -4842,12 +8867,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B955"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:B1416"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" customWidth="1"/>
+    <col min="2" max="2" width="134.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.42578125" customWidth="1"/>
     <col min="4" max="26" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10875,208 +14900,5310 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="754" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="755" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="756" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="757" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="758" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="759" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="760" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="761" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="762" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="763" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="764" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="765" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="766" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="767" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="768" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="754" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A754" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B754" s="6" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A755" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B755" s="8" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A756" s="5" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B756" s="6" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A757" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B757" s="8" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A758" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B758" s="6" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A759" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B759" s="8" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A760" s="5" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B760" s="6" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A761" s="7" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B761" s="8" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A762" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B762" s="6" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A763" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B763" s="8" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A764" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B764" s="6" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A765" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B765" s="8" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A766" s="5" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B766" s="6" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A767" s="7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B767" s="8" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A768" s="5" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B768" s="6" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A769" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B769" s="8" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A770" s="5" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B770" s="6" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A771" s="7" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B771" s="8" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A772" s="5" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B772" s="6" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A773" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B773" s="8" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A774" s="5" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B774" s="6" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A775" s="7" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B775" s="8" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A776" s="5" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B776" s="6" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A777" s="7" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B777" s="8" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A778" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B778" s="6" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A779" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B779" s="8" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A780" s="5" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B780" s="6" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A781" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B781" s="8" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A782" s="5" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B782" s="6" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A783" s="7" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B783" s="8" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A784" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B784" s="6" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A785" s="7" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B785" s="8" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A786" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B786" s="6" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A787" s="7" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B787" s="8" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A788" s="5" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B788" s="6" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A789" s="7" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B789" s="8" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A790" s="5" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B790" s="6" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A791" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B791" s="8" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A792" s="5" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B792" s="6" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A793" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B793" s="8" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A794" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B794" s="6" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A795" s="7" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B795" s="8" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A796" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B796" s="6" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A797" s="7" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B797" s="8" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A798" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B798" s="6" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A799" s="7" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B799" s="8" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A800" s="5" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B800" s="6" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A801" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B801" s="8" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A802" s="5" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B802" s="6" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A803" s="7" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B803" s="8" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A804" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B804" s="6" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A805" s="7" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B805" s="8" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A806" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B806" s="6" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A807" s="7" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B807" s="8" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A808" s="5" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B808" s="6" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A809" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B809" s="8" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A810" s="5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B810" s="6" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A811" s="7" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B811" s="8" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A812" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B812" s="6" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A813" s="7" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B813" s="8" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A814" s="5" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B814" s="6" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A815" s="7" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B815" s="8" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A816" s="5" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B816" s="6" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A817" s="7" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B817" s="8" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A818" s="5" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B818" s="6" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A819" s="7" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B819" s="8" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A820" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B820" s="6" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A821" s="7" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B821" s="8" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A822" s="5" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B822" s="6" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A823" s="7" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B823" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A824" s="5" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B824" s="6" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A825" s="7" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B825" s="8" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A826" s="5" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B826" s="6" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A827" s="7" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B827" s="8" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A828" s="5" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B828" s="6" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A829" s="7" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B829" s="8" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A830" s="5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B830" s="6" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A831" s="7" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B831" s="8" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A832" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B832" s="6" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A833" s="7" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B833" s="8" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A834" s="5" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B834" s="6" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A835" s="7" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B835" s="8" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A836" s="5" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B836" s="6" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A837" s="7" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B837" s="8" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A838" s="5" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B838" s="6" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A839" s="7" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B839" s="8" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A840" s="5" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B840" s="6" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A841" s="7" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B841" s="8" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A842" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B842" s="6" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A843" s="7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B843" s="8" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A844" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B844" s="6" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A845" s="7" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B845" s="8" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A846" s="5" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B846" s="6" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A847" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B847" s="8" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A848" s="5" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B848" s="6" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="849" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A849" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B849" s="8" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="850" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A850" s="5" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B850" s="6" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A851" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B851" s="8" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="852" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A852" s="5" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B852" s="6" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A853" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B853" s="8" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A854" s="5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B854" s="6" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A855" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B855" s="8" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A856" s="5" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B856" s="6" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A857" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B857" s="8" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A858" s="5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B858" s="6" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A859" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B859" s="8" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A860" s="5" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B860" s="6" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A861" s="7" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B861" s="8" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="862" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A862" s="5" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B862" s="6" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A863" s="7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B863" s="8" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="864" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A864" s="5" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B864" s="6" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="865" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A865" s="7" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B865" s="8" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="866" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A866" s="5" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B866" s="6" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="867" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A867" s="7" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B867" s="8" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="868" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A868" s="5" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B868" s="6" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="869" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A869" s="7" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B869" s="8" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="870" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A870" s="5" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B870" s="6" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="871" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A871" s="7" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B871" s="8" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="872" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A872" s="5" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B872" s="6" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="873" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A873" s="7" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B873" s="8" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="874" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A874" s="5" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B874" s="6" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="875" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A875" s="7" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B875" s="8" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A876" s="5" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B876" s="6" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="877" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A877" s="7" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B877" s="8" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="878" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A878" s="5" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B878" s="6" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="879" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A879" s="7" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B879" s="8" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="880" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A880" s="5" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B880" s="6" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="881" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A881" s="7" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B881" s="8" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="882" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A882" s="5" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B882" s="6" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="883" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A883" s="7" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B883" s="8" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="884" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A884" s="5" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B884" s="6" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="885" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A885" s="7" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B885" s="8" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="886" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A886" s="5" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B886" s="6" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="887" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A887" s="7" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B887" s="8" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="888" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A888" s="5" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B888" s="6" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="889" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A889" s="7" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B889" s="8" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="890" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A890" s="5" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B890" s="6" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="891" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A891" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B891" s="8" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="892" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A892" s="5" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B892" s="6" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="893" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A893" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B893" s="8" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="894" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A894" s="5" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B894" s="6" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="895" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A895" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B895" s="8" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="896" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A896" s="5" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B896" s="6" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="897" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A897" s="7" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B897" s="8" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="898" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A898" s="5" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B898" s="6" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="899" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A899" s="7" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B899" s="8" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="900" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A900" s="5" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B900" s="6" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A901" s="7" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B901" s="8" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A902" s="5" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B902" s="6" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A903" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B903" s="8" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="904" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A904" s="5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B904" s="6" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="905" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A905" s="7" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B905" s="8" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="906" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A906" s="5" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B906" s="6" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="907" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A907" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B907" s="8" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="908" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A908" s="5" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B908" s="6" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="909" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A909" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B909" s="8" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="910" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A910" s="5" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B910" s="6" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="911" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A911" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B911" s="8" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="912" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A912" s="5" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B912" s="6" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="913" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A913" s="7" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B913" s="8" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="914" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A914" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B914" s="6" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="915" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A915" s="7" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B915" s="8" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="916" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A916" s="5" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B916" s="6" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="917" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A917" s="7" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B917" s="8" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="918" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A918" s="5" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B918" s="6" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="919" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A919" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B919" s="8" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="920" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A920" s="5" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B920" s="6" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="921" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A921" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B921" s="8" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="922" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A922" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B922" s="6" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="923" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A923" s="7" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B923" s="8" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="924" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A924" s="5" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B924" s="6" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="925" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A925" s="7" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B925" s="8" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="926" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A926" s="5" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B926" s="6" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="927" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A927" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B927" s="8" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="928" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A928" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B928" s="6" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="929" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A929" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B929" s="8" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A930" s="5" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B930" s="6" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="931" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A931" s="7" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B931" s="8" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="932" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A932" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B932" s="6" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A933" s="7" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B933" s="8" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="934" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A934" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B934" s="6" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="935" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A935" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B935" s="8" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="936" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A936" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B936" s="6" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="937" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A937" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B937" s="8" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="938" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A938" s="5" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B938" s="6" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="939" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A939" s="7" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B939" s="8" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="940" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A940" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B940" s="6" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="941" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A941" s="7" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B941" s="8" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="942" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A942" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B942" s="6" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="943" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A943" s="7" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B943" s="8" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="944" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A944" s="5" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B944" s="6" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="945" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A945" s="7" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B945" s="8" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="946" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A946" s="5" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B946" s="6" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="947" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A947" s="7" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B947" s="8" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="948" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A948" s="5" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B948" s="6" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="949" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A949" s="7" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B949" s="8" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="950" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A950" s="5" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B950" s="6" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="951" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A951" s="7" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B951" s="8" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="952" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A952" s="5" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B952" s="6" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="953" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A953" s="7" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B953" s="8" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="954" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A954" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B954" s="6" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="955" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A955" s="7" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B955" s="8" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="956" spans="1:2" ht="15" customHeight="1">
+      <c r="A956" s="5" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B956" s="6" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="957" spans="1:2" ht="15" customHeight="1">
+      <c r="A957" s="7" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B957" s="8" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="958" spans="1:2" ht="15" customHeight="1">
+      <c r="A958" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B958" s="6" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="959" spans="1:2" ht="15" customHeight="1">
+      <c r="A959" s="7" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B959" s="8" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="960" spans="1:2" ht="15" customHeight="1">
+      <c r="A960" s="5" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B960" s="6" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="961" spans="1:2" ht="15" customHeight="1">
+      <c r="A961" s="7" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B961" s="8" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="962" spans="1:2" ht="15" customHeight="1">
+      <c r="A962" s="5" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B962" s="6" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="963" spans="1:2" ht="15" customHeight="1">
+      <c r="A963" s="7" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B963" s="8" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="964" spans="1:2" ht="15" customHeight="1">
+      <c r="A964" s="5" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B964" s="6" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="965" spans="1:2" ht="15" customHeight="1">
+      <c r="A965" s="7" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B965" s="8" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="966" spans="1:2" ht="15" customHeight="1">
+      <c r="A966" s="5" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B966" s="6" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="967" spans="1:2" ht="15" customHeight="1">
+      <c r="A967" s="7" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B967" s="8" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="968" spans="1:2" ht="15" customHeight="1">
+      <c r="A968" s="5" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B968" s="6" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="969" spans="1:2" ht="15" customHeight="1">
+      <c r="A969" s="7" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B969" s="8" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="970" spans="1:2" ht="15" customHeight="1">
+      <c r="A970" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B970" s="6" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="971" spans="1:2" ht="15" customHeight="1">
+      <c r="A971" s="7" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B971" s="8" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="972" spans="1:2" ht="15" customHeight="1">
+      <c r="A972" s="5" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B972" s="6" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="973" spans="1:2" ht="15" customHeight="1">
+      <c r="A973" s="7" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B973" s="8" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="974" spans="1:2" ht="15" customHeight="1">
+      <c r="A974" s="5" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B974" s="6" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="975" spans="1:2" ht="15" customHeight="1">
+      <c r="A975" s="7" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B975" s="8" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="976" spans="1:2" ht="15" customHeight="1">
+      <c r="A976" s="5" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B976" s="6" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="977" spans="1:2" ht="15" customHeight="1">
+      <c r="A977" s="7" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B977" s="8" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="978" spans="1:2" ht="15" customHeight="1">
+      <c r="A978" s="5" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B978" s="6" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="979" spans="1:2" ht="15" customHeight="1">
+      <c r="A979" s="7" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B979" s="8" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="980" spans="1:2" ht="15" customHeight="1">
+      <c r="A980" s="5" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B980" s="6" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="981" spans="1:2" ht="15" customHeight="1">
+      <c r="A981" s="7" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B981" s="8" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="982" spans="1:2" ht="15" customHeight="1">
+      <c r="A982" s="5" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B982" s="6" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="983" spans="1:2" ht="15" customHeight="1">
+      <c r="A983" s="7" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B983" s="8" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="984" spans="1:2" ht="15" customHeight="1">
+      <c r="A984" s="5" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B984" s="6" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="985" spans="1:2" ht="15" customHeight="1">
+      <c r="A985" s="7" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B985" s="8" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="986" spans="1:2" ht="15" customHeight="1">
+      <c r="A986" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B986" s="6" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="987" spans="1:2" ht="15" customHeight="1">
+      <c r="A987" s="7" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B987" s="8" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="988" spans="1:2" ht="15" customHeight="1">
+      <c r="A988" s="5" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B988" s="6" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="989" spans="1:2" ht="15" customHeight="1">
+      <c r="A989" s="7" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B989" s="8" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="990" spans="1:2" ht="15" customHeight="1">
+      <c r="A990" s="5" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B990" s="6" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="991" spans="1:2" ht="15" customHeight="1">
+      <c r="A991" s="7" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B991" s="8" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="992" spans="1:2" ht="15" customHeight="1">
+      <c r="A992" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B992" s="6" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="993" spans="1:2" ht="15" customHeight="1">
+      <c r="A993" s="7" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B993" s="8" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="994" spans="1:2" ht="15" customHeight="1">
+      <c r="A994" s="5" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B994" s="6" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="995" spans="1:2" ht="15" customHeight="1">
+      <c r="A995" s="7" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B995" s="8" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="996" spans="1:2" ht="15" customHeight="1">
+      <c r="A996" s="5" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B996" s="6" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="997" spans="1:2" ht="15" customHeight="1">
+      <c r="A997" s="7" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B997" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="998" spans="1:2" ht="15" customHeight="1">
+      <c r="A998" s="5" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B998" s="6" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="999" spans="1:2" ht="15" customHeight="1">
+      <c r="A999" s="7" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B999" s="8" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:2" ht="15" customHeight="1">
+      <c r="A1000" s="5" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1000" s="6" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:2" ht="15" customHeight="1">
+      <c r="A1001" s="7" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1001" s="8" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:2" ht="15" customHeight="1">
+      <c r="A1002" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1002" s="6" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:2" ht="15" customHeight="1">
+      <c r="A1003" s="7" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1003" s="8" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:2" ht="15" customHeight="1">
+      <c r="A1004" s="5" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1004" s="6" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:2" ht="15" customHeight="1">
+      <c r="A1005" s="7" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1005" s="8" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:2" ht="15" customHeight="1">
+      <c r="A1006" s="5" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1006" s="6" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:2" ht="15" customHeight="1">
+      <c r="A1007" s="7" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1007" s="8" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:2" ht="15" customHeight="1">
+      <c r="A1008" s="5" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1008" s="6" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:2" ht="15" customHeight="1">
+      <c r="A1009" s="7" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1009" s="8" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:2" ht="15" customHeight="1">
+      <c r="A1010" s="5" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1010" s="6" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:2" ht="15" customHeight="1">
+      <c r="A1011" s="7" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1011" s="8" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:2" ht="15" customHeight="1">
+      <c r="A1012" s="5" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1012" s="6" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:2" ht="15" customHeight="1">
+      <c r="A1013" s="7" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B1013" s="8" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:2" ht="15" customHeight="1">
+      <c r="A1014" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1014" s="6" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:2" ht="15" customHeight="1">
+      <c r="A1015" s="7" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1015" s="8" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:2" ht="15" customHeight="1">
+      <c r="A1016" s="5" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B1016" s="6" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:2" ht="15" customHeight="1">
+      <c r="A1017" s="7" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1017" s="8" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:2" ht="15" customHeight="1">
+      <c r="A1018" s="5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1018" s="6" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:2" ht="15" customHeight="1">
+      <c r="A1019" s="7" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1019" s="8" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:2" ht="15" customHeight="1">
+      <c r="A1020" s="5" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1020" s="6" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:2" ht="15" customHeight="1">
+      <c r="A1021" s="7" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1021" s="8" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:2" ht="15" customHeight="1">
+      <c r="A1022" s="5" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1022" s="6" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:2" ht="15" customHeight="1">
+      <c r="A1023" s="7" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1023" s="8" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:2" ht="15" customHeight="1">
+      <c r="A1024" s="5" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1024" s="6" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:2" ht="15" customHeight="1">
+      <c r="A1025" s="7" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B1025" s="8" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:2" ht="15" customHeight="1">
+      <c r="A1026" s="5" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1026" s="6" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:2" ht="15" customHeight="1">
+      <c r="A1027" s="7" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1027" s="8" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:2" ht="15" customHeight="1">
+      <c r="A1028" s="5" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1028" s="6" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:2" ht="15" customHeight="1">
+      <c r="A1029" s="7" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1029" s="8" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:2" ht="15" customHeight="1">
+      <c r="A1030" s="5" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1030" s="6" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:2" ht="15" customHeight="1">
+      <c r="A1031" s="7" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1031" s="8" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:2" ht="15" customHeight="1">
+      <c r="A1032" s="5" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B1032" s="6" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:2" ht="15" customHeight="1">
+      <c r="A1033" s="7" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1033" s="8" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:2" ht="15" customHeight="1">
+      <c r="A1034" s="5" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1034" s="6" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:2" ht="15" customHeight="1">
+      <c r="A1035" s="7" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B1035" s="8" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:2" ht="15" customHeight="1">
+      <c r="A1036" s="5" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1036" s="6" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:2" ht="15" customHeight="1">
+      <c r="A1037" s="7" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1037" s="8" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:2" ht="15" customHeight="1">
+      <c r="A1038" s="5" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B1038" s="6" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:2" ht="15" customHeight="1">
+      <c r="A1039" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1039" s="8" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:2" ht="15" customHeight="1">
+      <c r="A1040" s="5" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B1040" s="6" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:2" ht="15" customHeight="1">
+      <c r="A1041" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B1041" s="8" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:2" ht="15" customHeight="1">
+      <c r="A1042" s="5" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1042" s="6" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:2" ht="15" customHeight="1">
+      <c r="A1043" s="7" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1043" s="8" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:2" ht="15" customHeight="1">
+      <c r="A1044" s="5" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B1044" s="6" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:2" ht="15" customHeight="1">
+      <c r="A1045" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1045" s="8" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:2" ht="15" customHeight="1">
+      <c r="A1046" s="5" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1046" s="6" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:2" ht="15" customHeight="1">
+      <c r="A1047" s="7" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1047" s="8" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:2" ht="15" customHeight="1">
+      <c r="A1048" s="5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1048" s="6" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:2" ht="15" customHeight="1">
+      <c r="A1049" s="7" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1049" s="8" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:2" ht="15" customHeight="1">
+      <c r="A1050" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1050" s="6" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:2" ht="15" customHeight="1">
+      <c r="A1051" s="7" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1051" s="8" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:2" ht="15" customHeight="1">
+      <c r="A1052" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1052" s="6" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:2" ht="15" customHeight="1">
+      <c r="A1053" s="7" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1053" s="8" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:2" ht="15" customHeight="1">
+      <c r="A1054" s="5" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1054" s="6" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:2" ht="15" customHeight="1">
+      <c r="A1055" s="7" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1055" s="8" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:2" ht="15" customHeight="1">
+      <c r="A1056" s="5" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1056" s="6" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:2" ht="15" customHeight="1">
+      <c r="A1057" s="7" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1057" s="8" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:2" ht="15" customHeight="1">
+      <c r="A1058" s="5" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B1058" s="6" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:2" ht="15" customHeight="1">
+      <c r="A1059" s="7" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B1059" s="8" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:2" ht="15" customHeight="1">
+      <c r="A1060" s="5" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1060" s="6" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:2" ht="15" customHeight="1">
+      <c r="A1061" s="7" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1061" s="8" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:2" ht="15" customHeight="1">
+      <c r="A1062" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1062" s="6" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:2" ht="15" customHeight="1">
+      <c r="A1063" s="7" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1063" s="8" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:2" ht="15" customHeight="1">
+      <c r="A1064" s="5" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B1064" s="6" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:2" ht="15" customHeight="1">
+      <c r="A1065" s="7" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1065" s="8" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:2" ht="15" customHeight="1">
+      <c r="A1066" s="5" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1066" s="6" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:2" ht="15" customHeight="1">
+      <c r="A1067" s="7" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1067" s="8" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:2" ht="15" customHeight="1">
+      <c r="A1068" s="5" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1068" s="6" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:2" ht="15" customHeight="1">
+      <c r="A1069" s="7" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1069" s="8" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:2" ht="15" customHeight="1">
+      <c r="A1070" s="5" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1070" s="6" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:2" ht="15" customHeight="1">
+      <c r="A1071" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1071" s="8" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:2" ht="15" customHeight="1">
+      <c r="A1072" s="5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1072" s="6" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:2" ht="15" customHeight="1">
+      <c r="A1073" s="7" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1073" s="8" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:2" ht="15" customHeight="1">
+      <c r="A1074" s="5" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1074" s="6" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:2" ht="15" customHeight="1">
+      <c r="A1075" s="7" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1075" s="8" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:2" ht="15" customHeight="1">
+      <c r="A1076" s="5" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1076" s="6" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:2" ht="15" customHeight="1">
+      <c r="A1077" s="7" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1077" s="8" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:2" ht="15" customHeight="1">
+      <c r="A1078" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1078" s="6" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:2" ht="15" customHeight="1">
+      <c r="A1079" s="7" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1079" s="8" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:2" ht="15" customHeight="1">
+      <c r="A1080" s="5" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1080" s="6" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:2" ht="15" customHeight="1">
+      <c r="A1081" s="7" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1081" s="8" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:2" ht="15" customHeight="1">
+      <c r="A1082" s="5" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1082" s="6" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:2" ht="15" customHeight="1">
+      <c r="A1083" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1083" s="8" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:2" ht="15" customHeight="1">
+      <c r="A1084" s="5" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1084" s="6" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:2" ht="15" customHeight="1">
+      <c r="A1085" s="7" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1085" s="8" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:2" ht="15" customHeight="1">
+      <c r="A1086" s="5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1086" s="6" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:2" ht="15" customHeight="1">
+      <c r="A1087" s="7" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B1087" s="8" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:2" ht="15" customHeight="1">
+      <c r="A1088" s="5" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1088" s="6" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:2" ht="15" customHeight="1">
+      <c r="A1089" s="7" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1089" s="8" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:2" ht="15" customHeight="1">
+      <c r="A1090" s="5" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B1090" s="6" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:2" ht="15" customHeight="1">
+      <c r="A1091" s="7" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1091" s="8" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:2" ht="15" customHeight="1">
+      <c r="A1092" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1092" s="6" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:2" ht="15" customHeight="1">
+      <c r="A1093" s="7" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1093" s="8" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:2" ht="15" customHeight="1">
+      <c r="A1094" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1094" s="6" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:2" ht="15" customHeight="1">
+      <c r="A1095" s="7" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1095" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:2" ht="15" customHeight="1">
+      <c r="A1096" s="5" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1096" s="6" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:2" ht="15" customHeight="1">
+      <c r="A1097" s="7" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1097" s="8" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:2" ht="15" customHeight="1">
+      <c r="A1098" s="5" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1098" s="6" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:2" ht="15" customHeight="1">
+      <c r="A1099" s="7" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1099" s="8" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:2" ht="15" customHeight="1">
+      <c r="A1100" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B1100" s="6" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:2" ht="15" customHeight="1">
+      <c r="A1101" s="7" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1101" s="8" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:2" ht="15" customHeight="1">
+      <c r="A1102" s="5" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1102" s="6" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:2" ht="15" customHeight="1">
+      <c r="A1103" s="7" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1103" s="8" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:2" ht="15" customHeight="1">
+      <c r="A1104" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1104" s="6" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:2" ht="15" customHeight="1">
+      <c r="A1105" s="7" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1105" s="8" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:2" ht="15" customHeight="1">
+      <c r="A1106" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1106" s="6" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:2" ht="15" customHeight="1">
+      <c r="A1107" s="7" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1107" s="8" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:2" ht="15" customHeight="1">
+      <c r="A1108" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1108" s="6" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:2" ht="15" customHeight="1">
+      <c r="A1109" s="7" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1109" s="8" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:2" ht="15" customHeight="1">
+      <c r="A1110" s="5" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1110" s="6" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:2" ht="15" customHeight="1">
+      <c r="A1111" s="7" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1111" s="8" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:2" ht="15" customHeight="1">
+      <c r="A1112" s="5" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1112" s="6" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:2" ht="15" customHeight="1">
+      <c r="A1113" s="7" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1113" s="8" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:2" ht="15" customHeight="1">
+      <c r="A1114" s="5" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1114" s="6" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:2" ht="15" customHeight="1">
+      <c r="A1115" s="7" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1115" s="8" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:2" ht="15" customHeight="1">
+      <c r="A1116" s="5" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1116" s="6" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:2" ht="15" customHeight="1">
+      <c r="A1117" s="7" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1117" s="8" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:2" ht="15" customHeight="1">
+      <c r="A1118" s="5" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1118" s="6" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:2" ht="15" customHeight="1">
+      <c r="A1119" s="7" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1119" s="8" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:2" ht="15" customHeight="1">
+      <c r="A1120" s="5" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1120" s="6" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:2" ht="15" customHeight="1">
+      <c r="A1121" s="7" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1121" s="8" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:2" ht="15" customHeight="1">
+      <c r="A1122" s="5" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B1122" s="6" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:2" ht="15" customHeight="1">
+      <c r="A1123" s="7" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1123" s="8" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:2" ht="15" customHeight="1">
+      <c r="A1124" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1124" s="6" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:2" ht="15" customHeight="1">
+      <c r="A1125" s="7" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B1125" s="8" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:2" ht="15" customHeight="1">
+      <c r="A1126" s="5" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1126" s="6" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:2" ht="15" customHeight="1">
+      <c r="A1127" s="7" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B1127" s="8" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:2" ht="15" customHeight="1">
+      <c r="A1128" s="5" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1128" s="6" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:2" ht="15" customHeight="1">
+      <c r="A1129" s="7" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1129" s="8" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:2" ht="15" customHeight="1">
+      <c r="A1130" s="5" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B1130" s="6" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:2" ht="15" customHeight="1">
+      <c r="A1131" s="7" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B1131" s="8" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:2" ht="15" customHeight="1">
+      <c r="A1132" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1132" s="6" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:2" ht="15" customHeight="1">
+      <c r="A1133" s="7" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1133" s="8" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:2" ht="15" customHeight="1">
+      <c r="A1134" s="5" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B1134" s="6" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:2" ht="15" customHeight="1">
+      <c r="A1135" s="7" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1135" s="8" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:2" ht="15" customHeight="1">
+      <c r="A1136" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B1136" s="6" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:2" ht="15" customHeight="1">
+      <c r="A1137" s="7" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B1137" s="8" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:2" ht="15" customHeight="1">
+      <c r="A1138" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1138" s="6" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:2" ht="15" customHeight="1">
+      <c r="A1139" s="7" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B1139" s="8" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:2" ht="15" customHeight="1">
+      <c r="A1140" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B1140" s="6" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:2" ht="15" customHeight="1">
+      <c r="A1141" s="7" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B1141" s="8" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:2" ht="15" customHeight="1">
+      <c r="A1142" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B1142" s="6" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:2" ht="15" customHeight="1">
+      <c r="A1143" s="7" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1143" s="8" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:2" ht="15" customHeight="1">
+      <c r="A1144" s="5" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B1144" s="6" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:2" ht="15" customHeight="1">
+      <c r="A1145" s="7" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B1145" s="8" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:2" ht="15" customHeight="1">
+      <c r="A1146" s="5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B1146" s="6" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:2" ht="15" customHeight="1">
+      <c r="A1147" s="7" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1147" s="8" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:2" ht="15" customHeight="1">
+      <c r="A1148" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1148" s="6" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:2" ht="15" customHeight="1">
+      <c r="A1149" s="7" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B1149" s="8" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:2" ht="15" customHeight="1">
+      <c r="A1150" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1150" s="6" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:2" ht="15" customHeight="1">
+      <c r="A1151" s="7" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B1151" s="8" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:2" ht="15" customHeight="1">
+      <c r="A1152" s="5" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B1152" s="6" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:2" ht="15" customHeight="1">
+      <c r="A1153" s="7" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1153" s="8" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:2" ht="15" customHeight="1">
+      <c r="A1154" s="5" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B1154" s="6" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:2" ht="15" customHeight="1">
+      <c r="A1155" s="7" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1155" s="8" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:2" ht="15" customHeight="1">
+      <c r="A1156" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1156" s="6" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:2" ht="15" customHeight="1">
+      <c r="A1157" s="7" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B1157" s="8" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:2" ht="15" customHeight="1">
+      <c r="A1158" s="5" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B1158" s="6" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:2" ht="15" customHeight="1">
+      <c r="A1159" s="7" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1159" s="8" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:2" ht="15" customHeight="1">
+      <c r="A1160" s="5" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B1160" s="6" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:2" ht="15" customHeight="1">
+      <c r="A1161" s="7" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B1161" s="8" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:2" ht="15" customHeight="1">
+      <c r="A1162" s="5" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B1162" s="6" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:2" ht="15" customHeight="1">
+      <c r="A1163" s="7" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B1163" s="8" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:2" ht="15" customHeight="1">
+      <c r="A1164" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B1164" s="6" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:2" ht="15" customHeight="1">
+      <c r="A1165" s="7" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B1165" s="8" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:2" ht="15" customHeight="1">
+      <c r="A1166" s="5" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B1166" s="6" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:2" ht="15" customHeight="1">
+      <c r="A1167" s="7" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B1167" s="8" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:2" ht="15" customHeight="1">
+      <c r="A1168" s="5" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1168" s="6" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:2" ht="15" customHeight="1">
+      <c r="A1169" s="7" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B1169" s="8" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:2" ht="15" customHeight="1">
+      <c r="A1170" s="5" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B1170" s="6" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:2" ht="15" customHeight="1">
+      <c r="A1171" s="7" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B1171" s="8" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:2" ht="15" customHeight="1">
+      <c r="A1172" s="5" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B1172" s="6" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:2" ht="15" customHeight="1">
+      <c r="A1173" s="7" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B1173" s="8" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:2" ht="15" customHeight="1">
+      <c r="A1174" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B1174" s="6" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2" ht="15" customHeight="1">
+      <c r="A1175" s="7" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B1175" s="8" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2" ht="15" customHeight="1">
+      <c r="A1176" s="5" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B1176" s="6" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2" ht="15" customHeight="1">
+      <c r="A1177" s="7" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1177" s="8" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:2" ht="15" customHeight="1">
+      <c r="A1178" s="5" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B1178" s="6" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:2" ht="15" customHeight="1">
+      <c r="A1179" s="7" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B1179" s="8" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2" ht="15" customHeight="1">
+      <c r="A1180" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1180" s="6" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2" ht="15" customHeight="1">
+      <c r="A1181" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B1181" s="8" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2" ht="15" customHeight="1">
+      <c r="A1182" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="B1182" s="6" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2" ht="15" customHeight="1">
+      <c r="A1183" s="7" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B1183" s="8" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2" ht="15" customHeight="1">
+      <c r="A1184" s="5" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B1184" s="6" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2" ht="15" customHeight="1">
+      <c r="A1185" s="7" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1185" s="8" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2" ht="15" customHeight="1">
+      <c r="A1186" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B1186" s="6" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2" ht="15" customHeight="1">
+      <c r="A1187" s="7" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B1187" s="8" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:2" ht="15" customHeight="1">
+      <c r="A1188" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B1188" s="6" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:2" ht="15" customHeight="1">
+      <c r="A1189" s="7" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1189" s="8" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:2" ht="15" customHeight="1">
+      <c r="A1190" s="5" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B1190" s="6" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2" ht="15" customHeight="1">
+      <c r="A1191" s="7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B1191" s="8" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2" ht="15" customHeight="1">
+      <c r="A1192" s="5" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1192" s="6" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2" ht="15" customHeight="1">
+      <c r="A1193" s="7" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B1193" s="8" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:2" ht="15" customHeight="1">
+      <c r="A1194" s="5" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B1194" s="6" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2" ht="15" customHeight="1">
+      <c r="A1195" s="7" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B1195" s="8" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2" ht="15" customHeight="1">
+      <c r="A1196" s="5" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B1196" s="6" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2" ht="15" customHeight="1">
+      <c r="A1197" s="7" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B1197" s="8" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2" ht="15" customHeight="1">
+      <c r="A1198" s="5" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B1198" s="6" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2" ht="15" customHeight="1">
+      <c r="A1199" s="7" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B1199" s="8" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:2" ht="15" customHeight="1">
+      <c r="A1200" s="5" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B1200" s="6" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:2" ht="15" customHeight="1">
+      <c r="A1201" s="7" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B1201" s="8" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:2" ht="15" customHeight="1">
+      <c r="A1202" s="5" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B1202" s="6" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:2" ht="15" customHeight="1">
+      <c r="A1203" s="7" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B1203" s="8" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:2" ht="15" customHeight="1">
+      <c r="A1204" s="5" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B1204" s="6" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:2" ht="15" customHeight="1">
+      <c r="A1205" s="7" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B1205" s="8" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2" ht="15" customHeight="1">
+      <c r="A1206" s="5" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B1206" s="6" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2" ht="15" customHeight="1">
+      <c r="A1207" s="7" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1207" s="8" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2" ht="15" customHeight="1">
+      <c r="A1208" s="5" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B1208" s="6" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2" ht="15" customHeight="1">
+      <c r="A1209" s="7" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B1209" s="8" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2" ht="15" customHeight="1">
+      <c r="A1210" s="5" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B1210" s="6" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2" ht="15" customHeight="1">
+      <c r="A1211" s="7" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B1211" s="8" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2" ht="15" customHeight="1">
+      <c r="A1212" s="5" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B1212" s="6" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:2" ht="15" customHeight="1">
+      <c r="A1213" s="7" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B1213" s="8" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:2" ht="15" customHeight="1">
+      <c r="A1214" s="5" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1214" s="6" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:2" ht="15" customHeight="1">
+      <c r="A1215" s="7" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1215" s="8" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:2" ht="15" customHeight="1">
+      <c r="A1216" s="5" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1216" s="6" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:2" ht="15" customHeight="1">
+      <c r="A1217" s="7" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B1217" s="8" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:2" ht="15" customHeight="1">
+      <c r="A1218" s="5" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B1218" s="6" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:2" ht="15" customHeight="1">
+      <c r="A1219" s="7" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B1219" s="8" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:2" ht="15" customHeight="1">
+      <c r="A1220" s="5" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B1220" s="6" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:2" ht="15" customHeight="1">
+      <c r="A1221" s="7" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1221" s="8" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:2" ht="15" customHeight="1">
+      <c r="A1222" s="5" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B1222" s="6" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:2" ht="15" customHeight="1">
+      <c r="A1223" s="7" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B1223" s="8" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:2" ht="15" customHeight="1">
+      <c r="A1224" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1224" s="6" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:2" ht="15" customHeight="1">
+      <c r="A1225" s="7" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1225" s="8" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:2" ht="15" customHeight="1">
+      <c r="A1226" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B1226" s="6" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:2" ht="15" customHeight="1">
+      <c r="A1227" s="7" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B1227" s="8" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:2" ht="15" customHeight="1">
+      <c r="A1228" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B1228" s="6" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:2" ht="15" customHeight="1">
+      <c r="A1229" s="7" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B1229" s="8" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:2" ht="15" customHeight="1">
+      <c r="A1230" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B1230" s="6" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:2" ht="15" customHeight="1">
+      <c r="A1231" s="7" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B1231" s="8" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:2" ht="15" customHeight="1">
+      <c r="A1232" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B1232" s="6" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:2" ht="15" customHeight="1">
+      <c r="A1233" s="7" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B1233" s="8" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:2" ht="15" customHeight="1">
+      <c r="A1234" s="5" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B1234" s="6" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:2" ht="15" customHeight="1">
+      <c r="A1235" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B1235" s="8" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:2" ht="15" customHeight="1">
+      <c r="A1236" s="5" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B1236" s="6" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:2" ht="15" customHeight="1">
+      <c r="A1237" s="7" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B1237" s="8" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:2" ht="15" customHeight="1">
+      <c r="A1238" s="5" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B1238" s="6" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:2" ht="15" customHeight="1">
+      <c r="A1239" s="7" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B1239" s="8" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:2" ht="15" customHeight="1">
+      <c r="A1240" s="5" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B1240" s="6" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:2" ht="15" customHeight="1">
+      <c r="A1241" s="7" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B1241" s="8" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:2" ht="15" customHeight="1">
+      <c r="A1242" s="5" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B1242" s="6" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:2" ht="15" customHeight="1">
+      <c r="A1243" s="7" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B1243" s="8" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:2" ht="15" customHeight="1">
+      <c r="A1244" s="5" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B1244" s="6" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:2" ht="15" customHeight="1">
+      <c r="A1245" s="7" t="s">
+        <v>2487</v>
+      </c>
+      <c r="B1245" s="8" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:2" ht="15" customHeight="1">
+      <c r="A1246" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B1246" s="6" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:2" ht="15" customHeight="1">
+      <c r="A1247" s="7" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B1247" s="8" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:2" ht="15" customHeight="1">
+      <c r="A1248" s="5" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B1248" s="6" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:2" ht="15" customHeight="1">
+      <c r="A1249" s="7" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B1249" s="8" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:2" ht="15" customHeight="1">
+      <c r="A1250" s="5" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B1250" s="6" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:2" ht="15" customHeight="1">
+      <c r="A1251" s="7" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B1251" s="8" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:2" ht="15" customHeight="1">
+      <c r="A1252" s="5" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B1252" s="6" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:2" ht="15" customHeight="1">
+      <c r="A1253" s="7" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B1253" s="8" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:2" ht="15" customHeight="1">
+      <c r="A1254" s="5" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B1254" s="6" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:2" ht="15" customHeight="1">
+      <c r="A1255" s="7" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B1255" s="8" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:2" ht="15" customHeight="1">
+      <c r="A1256" s="5" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B1256" s="6" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2" ht="15" customHeight="1">
+      <c r="A1257" s="7" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B1257" s="8" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:2" ht="15" customHeight="1">
+      <c r="A1258" s="5" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B1258" s="6" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:2" ht="15" customHeight="1">
+      <c r="A1259" s="7" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B1259" s="8" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:2" ht="15" customHeight="1">
+      <c r="A1260" s="5" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B1260" s="6" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:2" ht="15" customHeight="1">
+      <c r="A1261" s="7" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B1261" s="8" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:2" ht="15" customHeight="1">
+      <c r="A1262" s="5" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B1262" s="6" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:2" ht="15" customHeight="1">
+      <c r="A1263" s="7" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B1263" s="8" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:2" ht="15" customHeight="1">
+      <c r="A1264" s="5" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B1264" s="6" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:2" ht="15" customHeight="1">
+      <c r="A1265" s="7" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B1265" s="8" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:2" ht="15" customHeight="1">
+      <c r="A1266" s="5" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B1266" s="6" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:2" ht="15" customHeight="1">
+      <c r="A1267" s="7" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B1267" s="8" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:2" ht="15" customHeight="1">
+      <c r="A1268" s="5" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B1268" s="6" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:2" ht="15" customHeight="1">
+      <c r="A1269" s="7" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B1269" s="8" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:2" ht="15" customHeight="1">
+      <c r="A1270" s="5" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B1270" s="6" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:2" ht="15" customHeight="1">
+      <c r="A1271" s="7" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B1271" s="8" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:2" ht="15" customHeight="1">
+      <c r="A1272" s="5" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B1272" s="6" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:2" ht="15" customHeight="1">
+      <c r="A1273" s="7" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B1273" s="8" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:2" ht="15" customHeight="1">
+      <c r="A1274" s="5" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B1274" s="6" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:2" ht="15" customHeight="1">
+      <c r="A1275" s="7" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B1275" s="8" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:2" ht="15" customHeight="1">
+      <c r="A1276" s="5" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B1276" s="6" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:2" ht="15" customHeight="1">
+      <c r="A1277" s="7" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B1277" s="8" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:2" ht="15" customHeight="1">
+      <c r="A1278" s="5" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B1278" s="6" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:2" ht="15" customHeight="1">
+      <c r="A1279" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B1279" s="8" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:2" ht="15" customHeight="1">
+      <c r="A1280" s="5" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B1280" s="6" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:2" ht="15" customHeight="1">
+      <c r="A1281" s="7" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B1281" s="8" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:2" ht="15" customHeight="1">
+      <c r="A1282" s="5" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B1282" s="6" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:2" ht="15" customHeight="1">
+      <c r="A1283" s="7" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B1283" s="8" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:2" ht="15" customHeight="1">
+      <c r="A1284" s="5" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B1284" s="6" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:2" ht="15" customHeight="1">
+      <c r="A1285" s="7" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B1285" s="8" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:2" ht="15" customHeight="1">
+      <c r="A1286" s="5" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B1286" s="6" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:2" ht="15" customHeight="1">
+      <c r="A1287" s="7" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B1287" s="8" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:2" ht="15" customHeight="1">
+      <c r="A1288" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B1288" s="6" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:2" ht="15" customHeight="1">
+      <c r="A1289" s="7" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B1289" s="8" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:2" ht="15" customHeight="1">
+      <c r="A1290" s="5" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B1290" s="6" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:2" ht="15" customHeight="1">
+      <c r="A1291" s="7" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B1291" s="8" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:2" ht="15" customHeight="1">
+      <c r="A1292" s="5" t="s">
+        <v>2581</v>
+      </c>
+      <c r="B1292" s="6" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:2" ht="15" customHeight="1">
+      <c r="A1293" s="7" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B1293" s="8" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:2" ht="15" customHeight="1">
+      <c r="A1294" s="5" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B1294" s="6" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:2" ht="15" customHeight="1">
+      <c r="A1295" s="7" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B1295" s="8" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:2" ht="15" customHeight="1">
+      <c r="A1296" s="5" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B1296" s="6" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:2" ht="15" customHeight="1">
+      <c r="A1297" s="7" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B1297" s="8" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2" ht="15" customHeight="1">
+      <c r="A1298" s="5" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B1298" s="6" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2" ht="15" customHeight="1">
+      <c r="A1299" s="7" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B1299" s="8" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:2" ht="15" customHeight="1">
+      <c r="A1300" s="5" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B1300" s="6" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2" ht="15" customHeight="1">
+      <c r="A1301" s="7" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B1301" s="8" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2" ht="15" customHeight="1">
+      <c r="A1302" s="5" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B1302" s="6" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:2" ht="15" customHeight="1">
+      <c r="A1303" s="7" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B1303" s="8" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:2" ht="15" customHeight="1">
+      <c r="A1304" s="5" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B1304" s="6" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:2" ht="15" customHeight="1">
+      <c r="A1305" s="7" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B1305" s="8" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:2" ht="15" customHeight="1">
+      <c r="A1306" s="5" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B1306" s="6" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2" ht="15" customHeight="1">
+      <c r="A1307" s="7" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B1307" s="8" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2" ht="15" customHeight="1">
+      <c r="A1308" s="5" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B1308" s="6" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:2" ht="15" customHeight="1">
+      <c r="A1309" s="7" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B1309" s="8" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:2" ht="15" customHeight="1">
+      <c r="A1310" s="5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B1310" s="6" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:2" ht="15" customHeight="1">
+      <c r="A1311" s="7" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B1311" s="8" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:2" ht="15" customHeight="1">
+      <c r="A1312" s="5" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B1312" s="6" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:2" ht="15" customHeight="1">
+      <c r="A1313" s="7" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B1313" s="8" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:2" ht="15" customHeight="1">
+      <c r="A1314" s="5" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B1314" s="6" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:2" ht="15" customHeight="1">
+      <c r="A1315" s="7" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B1315" s="8" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2" ht="15" customHeight="1">
+      <c r="A1316" s="5" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B1316" s="6" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2" ht="15" customHeight="1">
+      <c r="A1317" s="7" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B1317" s="8" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:2" ht="15" customHeight="1">
+      <c r="A1318" s="5" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B1318" s="6" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2" ht="15" customHeight="1">
+      <c r="A1319" s="7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B1319" s="8" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2" ht="15" customHeight="1">
+      <c r="A1320" s="5" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B1320" s="6" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2" ht="15" customHeight="1">
+      <c r="A1321" s="7" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B1321" s="8" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2" ht="15" customHeight="1">
+      <c r="A1322" s="5" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B1322" s="6" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:2" ht="15" customHeight="1">
+      <c r="A1323" s="7" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B1323" s="8" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:2" ht="15" customHeight="1">
+      <c r="A1324" s="5" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B1324" s="6" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2" ht="15" customHeight="1">
+      <c r="A1325" s="7" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B1325" s="8" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2" ht="15" customHeight="1">
+      <c r="A1326" s="5" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B1326" s="6" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:2" ht="15" customHeight="1">
+      <c r="A1327" s="7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B1327" s="8" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:2" ht="15" customHeight="1">
+      <c r="A1328" s="5" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B1328" s="6" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:2" ht="15" customHeight="1">
+      <c r="A1329" s="7" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B1329" s="8" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:2" ht="15" customHeight="1">
+      <c r="A1330" s="5" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B1330" s="6" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:2" ht="15" customHeight="1">
+      <c r="A1331" s="7" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B1331" s="8" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:2" ht="15" customHeight="1">
+      <c r="A1332" s="5" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B1332" s="6" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:2" ht="15" customHeight="1">
+      <c r="A1333" s="7" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B1333" s="8" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:2" ht="15" customHeight="1">
+      <c r="A1334" s="5" t="s">
+        <v>2665</v>
+      </c>
+      <c r="B1334" s="6" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:2" ht="15" customHeight="1">
+      <c r="A1335" s="7" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B1335" s="8" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:2" ht="15" customHeight="1">
+      <c r="A1336" s="5" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B1336" s="6" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:2" ht="15" customHeight="1">
+      <c r="A1337" s="7" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B1337" s="8" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:2" ht="15" customHeight="1">
+      <c r="A1338" s="5" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B1338" s="6" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:2" ht="15" customHeight="1">
+      <c r="A1339" s="7" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B1339" s="8" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:2" ht="15" customHeight="1">
+      <c r="A1340" s="5" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B1340" s="6" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:2" ht="15" customHeight="1">
+      <c r="A1341" s="7" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B1341" s="8" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:2" ht="15" customHeight="1">
+      <c r="A1342" s="5" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B1342" s="6" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:2" ht="15" customHeight="1">
+      <c r="A1343" s="7" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B1343" s="8" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:2" ht="15" customHeight="1">
+      <c r="A1344" s="5" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B1344" s="6" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:2" ht="15" customHeight="1">
+      <c r="A1345" s="7" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B1345" s="8" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:2" ht="15" customHeight="1">
+      <c r="A1346" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="B1346" s="6" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:2" ht="15" customHeight="1">
+      <c r="A1347" s="7" t="s">
+        <v>2691</v>
+      </c>
+      <c r="B1347" s="8" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:2" ht="15" customHeight="1">
+      <c r="A1348" s="5" t="s">
+        <v>2693</v>
+      </c>
+      <c r="B1348" s="6" t="s">
+        <v>2694</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:2" ht="15" customHeight="1">
+      <c r="A1349" s="7" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B1349" s="8" t="s">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:2" ht="15" customHeight="1">
+      <c r="A1350" s="5" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B1350" s="6" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:2" ht="15" customHeight="1">
+      <c r="A1351" s="7" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B1351" s="8" t="s">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:2" ht="15" customHeight="1">
+      <c r="A1352" s="5" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B1352" s="6" t="s">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:2" ht="15" customHeight="1">
+      <c r="A1353" s="7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B1353" s="8" t="s">
+        <v>2704</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:2" ht="15" customHeight="1">
+      <c r="A1354" s="5" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B1354" s="6" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:2" ht="15" customHeight="1">
+      <c r="A1355" s="7" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B1355" s="8" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:2" ht="15" customHeight="1">
+      <c r="A1356" s="5" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B1356" s="6" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:2" ht="15" customHeight="1">
+      <c r="A1357" s="7" t="s">
+        <v>2711</v>
+      </c>
+      <c r="B1357" s="8" t="s">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:2" ht="15" customHeight="1">
+      <c r="A1358" s="5" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B1358" s="6" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:2" ht="15" customHeight="1">
+      <c r="A1359" s="7" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B1359" s="8" t="s">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:2" ht="15" customHeight="1">
+      <c r="A1360" s="5" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B1360" s="6" t="s">
+        <v>2718</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:2" ht="15" customHeight="1">
+      <c r="A1361" s="7" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B1361" s="8" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:2" ht="15" customHeight="1">
+      <c r="A1362" s="5" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B1362" s="6" t="s">
+        <v>2722</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:2" ht="15" customHeight="1">
+      <c r="A1363" s="7" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B1363" s="8" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:2" ht="15" customHeight="1">
+      <c r="A1364" s="5" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B1364" s="6" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:2" ht="15" customHeight="1">
+      <c r="A1365" s="7" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B1365" s="8" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:2" ht="15" customHeight="1">
+      <c r="A1366" s="5" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B1366" s="6" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:2" ht="15" customHeight="1">
+      <c r="A1367" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B1367" s="8" t="s">
+        <v>2732</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:2" ht="15" customHeight="1">
+      <c r="A1368" s="5" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B1368" s="6" t="s">
+        <v>2734</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:2" ht="15" customHeight="1">
+      <c r="A1369" s="7" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B1369" s="8" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:2" ht="15" customHeight="1">
+      <c r="A1370" s="5" t="s">
+        <v>2737</v>
+      </c>
+      <c r="B1370" s="6" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:2" ht="15" customHeight="1">
+      <c r="A1371" s="7" t="s">
+        <v>2739</v>
+      </c>
+      <c r="B1371" s="8" t="s">
+        <v>2740</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:2" ht="15" customHeight="1">
+      <c r="A1372" s="5" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B1372" s="6" t="s">
+        <v>2742</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:2" ht="15" customHeight="1">
+      <c r="A1373" s="7" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B1373" s="8" t="s">
+        <v>2744</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:2" ht="15" customHeight="1">
+      <c r="A1374" s="5" t="s">
+        <v>2745</v>
+      </c>
+      <c r="B1374" s="6" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:2" ht="15" customHeight="1">
+      <c r="A1375" s="7" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B1375" s="8" t="s">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:2" ht="15" customHeight="1">
+      <c r="A1376" s="5" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B1376" s="6" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:2" ht="15" customHeight="1">
+      <c r="A1377" s="7" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B1377" s="8" t="s">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:2" ht="15" customHeight="1">
+      <c r="A1378" s="5" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B1378" s="6" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:2" ht="15" customHeight="1">
+      <c r="A1379" s="7" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B1379" s="8" t="s">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:2" ht="15" customHeight="1">
+      <c r="A1380" s="5" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B1380" s="6" t="s">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:2" ht="15" customHeight="1">
+      <c r="A1381" s="7" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B1381" s="8" t="s">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:2" ht="15" customHeight="1">
+      <c r="A1382" s="5" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B1382" s="6" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:2" ht="15" customHeight="1">
+      <c r="A1383" s="7" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B1383" s="8" t="s">
+        <v>2764</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:2" ht="15" customHeight="1">
+      <c r="A1384" s="5" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B1384" s="6" t="s">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:2" ht="15" customHeight="1">
+      <c r="A1385" s="7" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B1385" s="8" t="s">
+        <v>2768</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:2" ht="15" customHeight="1">
+      <c r="A1386" s="5" t="s">
+        <v>2769</v>
+      </c>
+      <c r="B1386" s="6" t="s">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:2" ht="15" customHeight="1">
+      <c r="A1387" s="7" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B1387" s="8" t="s">
+        <v>2772</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:2" ht="15" customHeight="1">
+      <c r="A1388" s="5" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B1388" s="6" t="s">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:2" ht="15" customHeight="1">
+      <c r="A1389" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B1389" s="8" t="s">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:2" ht="15" customHeight="1">
+      <c r="A1390" s="5" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B1390" s="6" t="s">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:2" ht="15" customHeight="1">
+      <c r="A1391" s="7" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B1391" s="8" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:2" ht="15" customHeight="1">
+      <c r="A1392" s="5" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B1392" s="6" t="s">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:2" ht="15" customHeight="1">
+      <c r="A1393" s="7" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B1393" s="8" t="s">
+        <v>2784</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:2" ht="15" customHeight="1">
+      <c r="A1394" s="5" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B1394" s="6" t="s">
+        <v>2786</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:2" ht="15" customHeight="1">
+      <c r="A1395" s="7" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B1395" s="8" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:2" ht="15" customHeight="1">
+      <c r="A1396" s="5" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B1396" s="6" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:2" ht="15" customHeight="1">
+      <c r="A1397" s="7" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B1397" s="8" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:2" ht="15" customHeight="1">
+      <c r="A1398" s="5" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B1398" s="6" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:2" ht="15" customHeight="1">
+      <c r="A1399" s="7" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B1399" s="8" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:2" ht="15" customHeight="1">
+      <c r="A1400" s="5" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B1400" s="6" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:2" ht="15" customHeight="1">
+      <c r="A1401" s="7" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B1401" s="8" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:2" ht="15" customHeight="1">
+      <c r="A1402" s="5" t="s">
+        <v>2801</v>
+      </c>
+      <c r="B1402" s="6" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:2" ht="15" customHeight="1">
+      <c r="A1403" s="7" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B1403" s="8" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:2" ht="15" customHeight="1">
+      <c r="A1404" s="5" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B1404" s="6" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:2" ht="15" customHeight="1">
+      <c r="A1405" s="7" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B1405" s="8" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:2" ht="15" customHeight="1">
+      <c r="A1406" s="5" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B1406" s="6" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:2" ht="15" customHeight="1">
+      <c r="A1407" s="7" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1407" s="8" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:2" ht="15" customHeight="1">
+      <c r="A1408" s="5" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1408" s="6" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:2" ht="15" customHeight="1">
+      <c r="A1409" s="7" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B1409" s="8" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:2" ht="15" customHeight="1">
+      <c r="A1410" s="5" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B1410" s="6" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:2" ht="15" customHeight="1">
+      <c r="A1411" s="7" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B1411" s="8" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2" ht="15" customHeight="1">
+      <c r="A1412" s="5" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B1412" s="6" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:2" ht="15" customHeight="1">
+      <c r="A1413" s="7" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B1413" s="8" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:2" ht="15" customHeight="1">
+      <c r="A1414" s="5" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B1414" s="6" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:2" ht="15" customHeight="1">
+      <c r="A1415" s="7" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B1415" s="8" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2" ht="15" customHeight="1">
+      <c r="A1416" s="5" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B1416" s="6" t="s">
+        <v>2830</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
